--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBBF119-F928-4107-9A4C-5275A1C72FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2DC3A7-25A8-4D0D-A0D6-C37B7AEEF3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31080" yWindow="-1065" windowWidth="25170" windowHeight="15000" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5223" uniqueCount="1318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="1306">
   <si>
     <t>CoreMeta4Cat Vocabulary Reference Workbook</t>
   </si>
@@ -2678,15 +2678,6 @@
   <si>
     <t>Type of catalyst used (e.g. heterogeneous, homogeneous, biocatalyst).
 For heterogeneous catalysts, use voc4cat terms where available.</t>
-  </si>
-  <si>
-    <t>experiment pressure</t>
-  </si>
-  <si>
-    <t>VOC4CAT:0000118</t>
-  </si>
-  <si>
-    <t>Total pressure in the reactor during the experiment.</t>
   </si>
   <si>
     <t>feed composition range</t>
@@ -4076,33 +4067,6 @@
   </si>
   <si>
     <t>reaction conditions</t>
-  </si>
-  <si>
-    <t>reaction temperature</t>
-  </si>
-  <si>
-    <t>voc4cat:0007013</t>
-  </si>
-  <si>
-    <t>The temperature at which a chemical reaction is happening.</t>
-  </si>
-  <si>
-    <t>gas hourly space velocity</t>
-  </si>
-  <si>
-    <t>voc4cat:0007023</t>
-  </si>
-  <si>
-    <t>A physical quantity given by the volumetric flow entering a control volume divided by the size of the control volume; the quantity must be given in the unit 1/hour.  In heterogeneous catalysis the volume of the undiluted catalyst bed is used as characteristic control volume. In case of gases the flow at reference conditions (0°C, 100 kPa = 1 bar) is used.</t>
-  </si>
-  <si>
-    <t>weight hourly space velocity</t>
-  </si>
-  <si>
-    <t>voc4cat:0007046</t>
-  </si>
-  <si>
-    <t>A physical quantity given by the volumetric flow entering a catalytic reactor divided by the mass of the undiluted catalyst bed in this control volume. In case of gases the flow at reference conditions (0°C, 100 kPa = 1 bar) is used.</t>
   </si>
   <si>
     <t>reaction name</t>
@@ -4278,7 +4242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -4391,19 +4355,6 @@
       <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -4424,7 +4375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -4518,28 +4469,10 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4548,10 +4481,10 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -18628,7 +18561,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118C8BAC-9B70-4E7A-BFF0-9A2BB55A4E4D}">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -18677,10 +18610,10 @@
     </row>
     <row r="2" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -18691,17 +18624,23 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
@@ -18709,12 +18648,12 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
@@ -18724,668 +18663,648 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="I4" s="8" t="s">
+        <v>1292</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="33" t="s">
-        <v>861</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34" t="s">
-        <v>862</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="35" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="34" t="s">
         <v>1291</v>
       </c>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="27" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="33" t="s">
+        <v>1297</v>
+      </c>
       <c r="B6" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>54</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="38" t="s">
-        <v>1292</v>
-      </c>
-      <c r="J6" s="39" t="s">
-        <v>1293</v>
+      <c r="I6" s="35" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J6" s="36" t="s">
+        <v>1299</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
-        <v>864</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34" t="s">
-        <v>865</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>866</v>
+        <v>1300</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="27" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>1302</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A8" s="35" t="s">
-        <v>1294</v>
+      <c r="A8" s="37" t="s">
+        <v>1303</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="38" t="s">
-        <v>1295</v>
-      </c>
-      <c r="J8" s="39" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" s="40" t="s">
-        <v>1297</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30" t="s">
-        <v>1298</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B10" s="8" t="s">
         <v>103</v>
       </c>
+      <c r="C8" s="34" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="35" t="s">
+        <v>1304</v>
+      </c>
+      <c r="J8" s="36" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="8" t="s">
-        <v>51</v>
-      </c>
+      <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
-      <c r="I10" s="8" t="s">
-        <v>1304</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="35" t="s">
-        <v>1306</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="27" t="s">
-        <v>1307</v>
-      </c>
-      <c r="J11" s="28" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A12" s="35" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="41" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J12" s="42" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="35" t="s">
-        <v>1312</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="27" t="s">
-        <v>1313</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="43" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="41" t="s">
-        <v>1316</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8" t="s">
+      <c r="B12" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8" t="s">
+      <c r="F12" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J12" s="8" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
+    <row r="13" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8" t="s">
+      <c r="B13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8" t="s">
+      <c r="F13" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J13" s="8" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8" t="s">
+      <c r="B14" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8" t="s">
+      <c r="F14" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8" t="s">
         <v>859</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J14" s="8" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
+    <row r="15" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>861</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
         <v>864</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10" t="s">
+      <c r="B17" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>865</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="F17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B22" s="11" t="s">
+      <c r="J17" s="9" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>865</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>864</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A23" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9" t="s">
+      <c r="D18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>868</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9" t="s">
+    </row>
+    <row r="19" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
         <v>869</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="B19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="174" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>868</v>
-      </c>
-      <c r="B24" s="11" t="s">
+      <c r="F19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="C20" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9" t="s">
         <v>872</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
+      <c r="J20" s="9" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>874</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="13" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>874</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9" t="s">
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="20" t="s">
+        <v>1221</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>874</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="B26" s="9" t="s">
+      <c r="D23" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="20" t="s">
+        <v>1222</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A24" s="21" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>874</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22" t="s">
+        <v>1224</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="D26" s="9" t="s">
+      <c r="C25" s="11" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="24" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>874</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="24" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>874</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24" t="s">
+        <v>1237</v>
+      </c>
+      <c r="J28" s="24" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>877</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="13" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>877</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9" t="s">
-        <v>875</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="13" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>877</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11" t="s">
-        <v>878</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="13" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="14" t="s">
+      <c r="D31" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+    </row>
+    <row r="32" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="21" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>877</v>
       </c>
-      <c r="D28" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="20" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="13" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>877</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="20" t="s">
-        <v>1225</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A30" s="21" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>877</v>
-      </c>
-      <c r="D30" s="22" t="s">
+      <c r="D32" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J30" s="23" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
-        <v>1235</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-    </row>
-    <row r="33" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21" t="s">
+        <v>1241</v>
+      </c>
+      <c r="J32" s="21" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="24" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="B33" s="25" t="s">
         <v>70</v>
@@ -19400,86 +19319,82 @@
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
       <c r="H33" s="25"/>
-      <c r="I33" s="25" t="s">
-        <v>1234</v>
-      </c>
-      <c r="J33" s="26" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="24" t="s">
-        <v>1239</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="24" t="s">
+      <c r="I33" s="30"/>
+      <c r="J33" s="31"/>
+    </row>
+    <row r="34" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A34" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="D34" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24" t="s">
-        <v>1240</v>
-      </c>
-      <c r="J34" s="24" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
+      <c r="D34" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25" t="s">
+        <v>1248</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="25" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>877</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="25" t="s">
+        <v>1249</v>
+      </c>
+      <c r="J35" s="25" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
         <v>880</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B36" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11" t="s">
+      <c r="C36" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11" t="s">
         <v>881</v>
       </c>
-      <c r="J35" s="11" t="s">
+      <c r="J36" s="11" t="s">
         <v>882</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="13" t="s">
-        <v>1246</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13" t="s">
-        <v>1247</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="13" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>70</v>
@@ -19498,142 +19413,134 @@
       <c r="J37" s="13"/>
     </row>
     <row r="38" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="21" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="21" t="s">
+      <c r="A38" s="13" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>880</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="21" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>880</v>
+      </c>
+      <c r="D39" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21" t="s">
-        <v>1244</v>
-      </c>
-      <c r="J38" s="21" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="24" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="25" t="s">
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+    </row>
+    <row r="40" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="21" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>880</v>
       </c>
-      <c r="D39" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="31"/>
-    </row>
-    <row r="40" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A40" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="25" t="s">
+      <c r="D40" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+    </row>
+    <row r="41" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="21" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>880</v>
       </c>
-      <c r="D40" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25" t="s">
-        <v>1251</v>
-      </c>
-      <c r="J40" s="25" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="25" t="s">
-        <v>1250</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="25" t="s">
+      <c r="D41" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+    </row>
+    <row r="42" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A42" s="21" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="21" t="s">
         <v>880</v>
       </c>
-      <c r="D41" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="25" t="s">
-        <v>1252</v>
-      </c>
-      <c r="J41" s="25" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="11" t="s">
+      <c r="D42" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21" t="s">
+        <v>1256</v>
+      </c>
+      <c r="J42" s="21" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
         <v>883</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B43" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11" t="s">
+      <c r="C43" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11" t="s">
         <v>884</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="J43" s="11" t="s">
         <v>885</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="13" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>883</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
     </row>
     <row r="44" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="13" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>70</v>
@@ -19651,69 +19558,77 @@
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
     </row>
-    <row r="45" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="21" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="21" t="s">
+    <row r="45" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" s="13" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>883</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
+      <c r="D45" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13" t="s">
+        <v>1262</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>1263</v>
+      </c>
     </row>
     <row r="46" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="21" t="s">
-        <v>1261</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="21" t="s">
+      <c r="A46" s="13" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>883</v>
       </c>
-      <c r="D46" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
+      <c r="D46" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="21" t="s">
-        <v>1262</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="21" t="s">
+      <c r="A47" s="13" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="13" t="s">
         <v>883</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-    </row>
-    <row r="48" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="D47" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13" t="s">
+        <v>1265</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="21" t="s">
-        <v>1258</v>
+        <v>1268</v>
       </c>
       <c r="B48" s="21" t="s">
         <v>70</v>
@@ -19728,82 +19643,74 @@
       <c r="F48" s="21"/>
       <c r="G48" s="21"/>
       <c r="H48" s="21"/>
-      <c r="I48" s="21" t="s">
-        <v>1259</v>
-      </c>
-      <c r="J48" s="21" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A49" s="11" t="s">
+      <c r="I48" s="21"/>
+      <c r="J48" s="21"/>
+    </row>
+    <row r="49" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="32" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>883</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+    </row>
+    <row r="50" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B51" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11" t="s">
+      <c r="C51" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11" t="s">
         <v>887</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J51" s="11" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="13" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-    </row>
-    <row r="51" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A51" s="13" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13" t="s">
-        <v>1265</v>
-      </c>
-      <c r="J51" s="13" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A52" s="13" t="s">
-        <v>1270</v>
+        <v>1255</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>70</v>
@@ -19818,52 +19725,52 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
+      <c r="I52" s="13" t="s">
+        <v>1256</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>1257</v>
+      </c>
     </row>
     <row r="53" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="13" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="13" t="s">
+      <c r="A53" s="32" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="32" t="s">
         <v>886</v>
       </c>
-      <c r="D53" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13" t="s">
-        <v>1268</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>1269</v>
-      </c>
+      <c r="D53" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
     </row>
     <row r="54" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="32" t="s">
         <v>1271</v>
       </c>
-      <c r="B54" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" s="21" t="s">
+      <c r="B54" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="32" t="s">
         <v>886</v>
       </c>
-      <c r="D54" s="21" t="s">
+      <c r="D54" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
     </row>
     <row r="55" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="32" t="s">
@@ -19872,7 +19779,7 @@
       <c r="B55" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="32" t="s">
         <v>886</v>
       </c>
       <c r="D55" s="32" t="s">
@@ -19886,26 +19793,26 @@
       <c r="J55" s="32"/>
     </row>
     <row r="56" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J56" s="11"/>
-    </row>
-    <row r="57" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="32" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>886</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+    </row>
+    <row r="57" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
         <v>889</v>
       </c>
@@ -19913,7 +19820,7 @@
         <v>103</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
@@ -19927,9 +19834,9 @@
         <v>891</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="13" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="B58" s="13" t="s">
         <v>70</v>
@@ -19944,82 +19851,80 @@
       <c r="F58" s="13"/>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
-      <c r="I58" s="13" t="s">
-        <v>1259</v>
-      </c>
-      <c r="J58" s="13" t="s">
-        <v>1260</v>
-      </c>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
     </row>
     <row r="59" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="32" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B59" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C59" s="32" t="s">
+      <c r="A59" s="13" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>889</v>
       </c>
-      <c r="D59" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
+      <c r="D59" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
     </row>
     <row r="60" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="32" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B60" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" s="32" t="s">
+      <c r="A60" s="13" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="13" t="s">
         <v>889</v>
       </c>
-      <c r="D60" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-    </row>
-    <row r="61" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="32" t="s">
-        <v>1275</v>
-      </c>
-      <c r="B61" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="32" t="s">
-        <v>889</v>
-      </c>
-      <c r="D61" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="32"/>
-    </row>
-    <row r="62" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D60" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="11" t="s">
+        <v>892</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A62" s="32" t="s">
-        <v>1276</v>
+        <v>1255</v>
       </c>
       <c r="B62" s="32" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D62" s="32" t="s">
         <v>51</v>
@@ -20028,90 +19933,104 @@
       <c r="F62" s="32"/>
       <c r="G62" s="32"/>
       <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-    </row>
-    <row r="63" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="11" t="s">
+      <c r="I62" s="32" t="s">
+        <v>1256</v>
+      </c>
+      <c r="J62" s="32" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="32" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="32" t="s">
         <v>892</v>
       </c>
-      <c r="B63" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11" t="s">
-        <v>893</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="13" t="s">
+      <c r="D63" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="32"/>
+    </row>
+    <row r="64" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="32" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>892</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32" t="s">
+        <v>1278</v>
+      </c>
+      <c r="J64" s="32" t="s">
         <v>1279</v>
       </c>
-      <c r="B64" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="13" t="s">
+    </row>
+    <row r="65" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="32" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B65" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="32" t="s">
         <v>892</v>
       </c>
-      <c r="D64" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-    </row>
-    <row r="65" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="13" t="s">
-        <v>1277</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="13" t="s">
+      <c r="D65" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32" t="s">
+        <v>1281</v>
+      </c>
+      <c r="J65" s="32" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="32" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="32" t="s">
         <v>892</v>
       </c>
-      <c r="D65" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
-    </row>
-    <row r="66" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="13" t="s">
-        <v>1278</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>892</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
+      <c r="D66" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="32" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J66" s="32" t="s">
+        <v>1285</v>
+      </c>
     </row>
     <row r="67" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="11" t="s">
@@ -20121,7 +20040,7 @@
         <v>103</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
@@ -20135,247 +20054,106 @@
         <v>897</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A68" s="32" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B68" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" s="32" t="s">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="10" t="s">
+        <v>898</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="D68" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32" t="s">
-        <v>1259</v>
-      </c>
-      <c r="J68" s="32" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="32" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B69" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="32" t="s">
+      <c r="D68" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="10" t="s">
+        <v>899</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="10" t="s">
+        <v>901</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="D69" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="32"/>
-    </row>
-    <row r="70" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A70" s="32" t="s">
-        <v>1280</v>
-      </c>
-      <c r="B70" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" s="32" t="s">
+      <c r="D69" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>902</v>
+      </c>
+      <c r="J69" s="10" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A70" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="D70" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J70" s="32" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A71" s="32" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B71" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C71" s="32" t="s">
-        <v>895</v>
-      </c>
-      <c r="D71" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32" t="s">
-        <v>1284</v>
-      </c>
-      <c r="J71" s="32" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="32" t="s">
-        <v>1286</v>
-      </c>
-      <c r="B72" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C72" s="32" t="s">
-        <v>895</v>
-      </c>
-      <c r="D72" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32" t="s">
-        <v>1287</v>
-      </c>
-      <c r="J72" s="32" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="11" t="s">
-        <v>898</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>873</v>
-      </c>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11" t="s">
-        <v>899</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A74" s="10" t="s">
-        <v>901</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>898</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E74" s="10" t="s">
+      <c r="D70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F74" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10" t="s">
-        <v>902</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A75" s="10" t="s">
-        <v>904</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>898</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10" t="s">
-        <v>682</v>
-      </c>
-      <c r="I75" s="10" t="s">
+      <c r="F70" s="10"/>
+      <c r="G70" s="10"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="J75" s="10" t="s">
+      <c r="J70" s="10" t="s">
         <v>906</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A76" s="10" t="s">
-        <v>907</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>898</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10" t="s">
-        <v>908</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>909</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I28" r:id="rId1" display="voc4cat:0007254" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
-    <hyperlink ref="I29" r:id="rId2" display="voc4cat:0007255" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
-    <hyperlink ref="I33" r:id="rId3" display="voc4cat:0007258" xr:uid="{ECE0B83D-4C10-4937-A571-CB1A78F8D921}"/>
-    <hyperlink ref="I31" r:id="rId4" display="voc4cat:0007256" xr:uid="{B8B87E67-D090-44FF-99F3-C73E22B0384A}"/>
-    <hyperlink ref="I34" r:id="rId5" xr:uid="{AD38AF27-1671-4048-B637-B5B450D15DAD}"/>
-    <hyperlink ref="I40" r:id="rId6" xr:uid="{361B543E-C568-4568-8088-6E70DE9F3B27}"/>
-    <hyperlink ref="I41" r:id="rId7" xr:uid="{1719255A-01AA-4404-94C6-32789CDF8402}"/>
-    <hyperlink ref="I70" r:id="rId8" xr:uid="{67C09C0D-2279-4237-A447-58639A2AE5CC}"/>
-    <hyperlink ref="I6" r:id="rId9" xr:uid="{C3A1B5F3-77DF-47E1-BD93-D0135588BD53}"/>
-    <hyperlink ref="I8" r:id="rId10" xr:uid="{9E751171-F7FB-4E21-96BB-EC01369D266C}"/>
-    <hyperlink ref="I9" r:id="rId11" xr:uid="{5A2FE0DC-49A5-436A-AC4B-DF56A28B379B}"/>
-    <hyperlink ref="I2" r:id="rId12" xr:uid="{EE99F099-E6BA-477F-A260-88529C3F7434}"/>
-    <hyperlink ref="I10" r:id="rId13" xr:uid="{BDA420BA-A173-4F89-A841-856E53112396}"/>
-    <hyperlink ref="I14" r:id="rId14" xr:uid="{54581B7D-9C1E-4C15-887D-BA48A1859B95}"/>
-    <hyperlink ref="I13" r:id="rId15" xr:uid="{46577A97-6DF9-402F-BCAD-57196F467970}"/>
-    <hyperlink ref="I12" r:id="rId16" xr:uid="{11743F2A-1294-4AA1-9B68-D52B44449D93}"/>
-    <hyperlink ref="I11" r:id="rId17" xr:uid="{336B9A92-59C1-445E-9AD3-47037654015F}"/>
+    <hyperlink ref="I22" r:id="rId1" display="voc4cat:0007254" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
+    <hyperlink ref="I23" r:id="rId2" display="voc4cat:0007255" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
+    <hyperlink ref="I27" r:id="rId3" display="voc4cat:0007258" xr:uid="{ECE0B83D-4C10-4937-A571-CB1A78F8D921}"/>
+    <hyperlink ref="I25" r:id="rId4" display="voc4cat:0007256" xr:uid="{B8B87E67-D090-44FF-99F3-C73E22B0384A}"/>
+    <hyperlink ref="I28" r:id="rId5" xr:uid="{AD38AF27-1671-4048-B637-B5B450D15DAD}"/>
+    <hyperlink ref="I34" r:id="rId6" xr:uid="{361B543E-C568-4568-8088-6E70DE9F3B27}"/>
+    <hyperlink ref="I35" r:id="rId7" xr:uid="{1719255A-01AA-4404-94C6-32789CDF8402}"/>
+    <hyperlink ref="I64" r:id="rId8" xr:uid="{67C09C0D-2279-4237-A447-58639A2AE5CC}"/>
+    <hyperlink ref="I2" r:id="rId9" xr:uid="{EE99F099-E6BA-477F-A260-88529C3F7434}"/>
+    <hyperlink ref="I4" r:id="rId10" xr:uid="{BDA420BA-A173-4F89-A841-856E53112396}"/>
+    <hyperlink ref="I8" r:id="rId11" xr:uid="{54581B7D-9C1E-4C15-887D-BA48A1859B95}"/>
+    <hyperlink ref="I7" r:id="rId12" xr:uid="{46577A97-6DF9-402F-BCAD-57196F467970}"/>
+    <hyperlink ref="I6" r:id="rId13" xr:uid="{11743F2A-1294-4AA1-9B68-D52B44449D93}"/>
+    <hyperlink ref="I5" r:id="rId14" xr:uid="{336B9A92-59C1-445E-9AD3-47037654015F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20432,7 +20210,7 @@
     </row>
     <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>70</v>
@@ -20450,15 +20228,15 @@
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>70</v>
@@ -20468,7 +20246,7 @@
         <v>48</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>74</v>
@@ -20478,21 +20256,21 @@
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>48</v>
@@ -20502,21 +20280,21 @@
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>48</v>
@@ -20526,21 +20304,21 @@
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>54</v>
@@ -20553,24 +20331,24 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>54</v>
@@ -20584,21 +20362,21 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>54</v>
@@ -20611,24 +20389,24 @@
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>54</v>
@@ -20642,21 +20420,21 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>54</v>
@@ -20670,21 +20448,21 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>48</v>
@@ -20694,21 +20472,21 @@
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>54</v>
@@ -20722,21 +20500,21 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>54</v>
@@ -20750,21 +20528,21 @@
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>54</v>
@@ -20778,21 +20556,21 @@
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>54</v>
@@ -20806,21 +20584,21 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>48</v>
@@ -20830,21 +20608,21 @@
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>54</v>
@@ -20858,21 +20636,21 @@
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>54</v>
@@ -20885,24 +20663,24 @@
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="10" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>54</v>
@@ -20915,24 +20693,24 @@
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>54</v>
@@ -20946,21 +20724,21 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>54</v>
@@ -20973,24 +20751,24 @@
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>48</v>
@@ -21000,21 +20778,21 @@
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>54</v>
@@ -21027,24 +20805,24 @@
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>54</v>
@@ -21058,21 +20836,21 @@
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>54</v>
@@ -21085,24 +20863,24 @@
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>54</v>
@@ -21115,24 +20893,24 @@
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>54</v>
@@ -21146,21 +20924,21 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>48</v>
@@ -21170,21 +20948,21 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>54</v>
@@ -21198,21 +20976,21 @@
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>54</v>
@@ -21226,21 +21004,21 @@
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>54</v>
@@ -21254,21 +21032,21 @@
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>54</v>
@@ -21282,21 +21060,21 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>54</v>
@@ -21309,24 +21087,24 @@
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>54</v>
@@ -21340,21 +21118,21 @@
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>54</v>
@@ -21368,21 +21146,21 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>48</v>
@@ -21392,21 +21170,21 @@
       <c r="G36" s="11"/>
       <c r="H36" s="11"/>
       <c r="I36" s="11" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>54</v>
@@ -21420,21 +21198,21 @@
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>54</v>
@@ -21448,21 +21226,21 @@
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>54</v>
@@ -21475,30 +21253,30 @@
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>74</v>
@@ -21506,21 +21284,21 @@
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>54</v>
@@ -21534,21 +21312,21 @@
       <c r="G41" s="10"/>
       <c r="H41" s="10"/>
       <c r="I41" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>54</v>
@@ -21562,21 +21340,21 @@
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>48</v>
@@ -21586,21 +21364,21 @@
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>54</v>
@@ -21614,21 +21392,21 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>54</v>
@@ -21641,24 +21419,24 @@
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="10" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>54</v>
@@ -21672,21 +21450,21 @@
       <c r="G46" s="10"/>
       <c r="H46" s="10"/>
       <c r="I46" s="10" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>54</v>
@@ -21700,21 +21478,21 @@
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>54</v>
@@ -21728,21 +21506,21 @@
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
       <c r="I48" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>54</v>
@@ -21756,21 +21534,21 @@
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
       <c r="I49" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>54</v>
@@ -21783,24 +21561,24 @@
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>54</v>
@@ -21814,21 +21592,21 @@
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
       <c r="I51" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>54</v>
@@ -21842,21 +21620,21 @@
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
       <c r="I52" s="10" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>48</v>
@@ -21866,21 +21644,21 @@
       <c r="G53" s="11"/>
       <c r="H53" s="11"/>
       <c r="I53" s="11" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>54</v>
@@ -21894,21 +21672,21 @@
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
       <c r="I54" s="10" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>54</v>
@@ -21922,21 +21700,21 @@
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
       <c r="I55" s="10" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>54</v>
@@ -21950,21 +21728,21 @@
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
       <c r="I56" s="10" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>54</v>
@@ -21977,13 +21755,13 @@
       </c>
       <c r="G57" s="10"/>
       <c r="H57" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
@@ -21994,7 +21772,7 @@
         <v>70</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>54</v>
@@ -22010,13 +21788,13 @@
     </row>
     <row r="59" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>54</v>
@@ -22030,21 +21808,21 @@
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
       <c r="I59" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>54</v>
@@ -22058,21 +21836,21 @@
       <c r="G60" s="10"/>
       <c r="H60" s="10"/>
       <c r="I60" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>48</v>
@@ -22082,21 +21860,21 @@
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
       <c r="I61" s="11" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>54</v>
@@ -22110,21 +21888,21 @@
       <c r="G62" s="10"/>
       <c r="H62" s="10"/>
       <c r="I62" s="10" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>54</v>
@@ -22137,24 +21915,24 @@
       </c>
       <c r="G63" s="10"/>
       <c r="H63" s="10" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>54</v>
@@ -22167,24 +21945,24 @@
       </c>
       <c r="G64" s="10"/>
       <c r="H64" s="10" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>54</v>
@@ -22198,21 +21976,21 @@
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
       <c r="I65" s="10" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>54</v>
@@ -22226,21 +22004,21 @@
       <c r="G66" s="10"/>
       <c r="H66" s="10"/>
       <c r="I66" s="10" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>54</v>
@@ -22254,21 +22032,21 @@
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
       <c r="I67" s="10" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>54</v>
@@ -22282,21 +22060,21 @@
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
       <c r="I68" s="10" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>54</v>
@@ -22310,21 +22088,21 @@
       <c r="G69" s="10"/>
       <c r="H69" s="10"/>
       <c r="I69" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>54</v>
@@ -22338,21 +22116,21 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
       <c r="I70" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>48</v>
@@ -22362,21 +22140,21 @@
       <c r="G71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="11" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>54</v>
@@ -22390,27 +22168,27 @@
       <c r="G72" s="10"/>
       <c r="H72" s="10"/>
       <c r="I72" s="10" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>74</v>
@@ -22418,21 +22196,21 @@
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
       <c r="I73" s="10" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>54</v>
@@ -22446,21 +22224,21 @@
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
       <c r="I74" s="10" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>54</v>
@@ -22473,24 +22251,24 @@
       </c>
       <c r="G75" s="10"/>
       <c r="H75" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>54</v>
@@ -22504,21 +22282,21 @@
       <c r="G76" s="10"/>
       <c r="H76" s="10"/>
       <c r="I76" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>54</v>
@@ -22532,21 +22310,21 @@
       <c r="G77" s="10"/>
       <c r="H77" s="10"/>
       <c r="I77" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>54</v>
@@ -22559,24 +22337,24 @@
       </c>
       <c r="G78" s="10"/>
       <c r="H78" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>54</v>
@@ -22590,21 +22368,21 @@
       <c r="G79" s="10"/>
       <c r="H79" s="10"/>
       <c r="I79" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>54</v>
@@ -22618,21 +22396,21 @@
       <c r="G80" s="10"/>
       <c r="H80" s="10"/>
       <c r="I80" s="10" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" s="11" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>48</v>
@@ -22642,21 +22420,21 @@
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
       <c r="I81" s="11" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>54</v>
@@ -22670,21 +22448,21 @@
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="10" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>54</v>
@@ -22697,24 +22475,24 @@
       </c>
       <c r="G83" s="10"/>
       <c r="H83" s="10" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>54</v>
@@ -22728,21 +22506,21 @@
       <c r="G84" s="10"/>
       <c r="H84" s="10"/>
       <c r="I84" s="10" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>54</v>
@@ -22755,24 +22533,24 @@
       </c>
       <c r="G85" s="10"/>
       <c r="H85" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>54</v>
@@ -22785,24 +22563,24 @@
       </c>
       <c r="G86" s="10"/>
       <c r="H86" s="10" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>54</v>
@@ -22816,21 +22594,21 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="10" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>54</v>
@@ -22844,21 +22622,21 @@
       <c r="G88" s="10"/>
       <c r="H88" s="10"/>
       <c r="I88" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>54</v>
@@ -22872,21 +22650,21 @@
       <c r="G89" s="10"/>
       <c r="H89" s="10"/>
       <c r="I89" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" s="11" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>48</v>
@@ -22896,21 +22674,21 @@
       <c r="G90" s="11"/>
       <c r="H90" s="11"/>
       <c r="I90" s="11" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>54</v>
@@ -22924,21 +22702,21 @@
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
       <c r="I91" s="10" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>54</v>
@@ -22952,21 +22730,21 @@
       <c r="G92" s="10"/>
       <c r="H92" s="10"/>
       <c r="I92" s="10" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>54</v>
@@ -22979,24 +22757,24 @@
       </c>
       <c r="G93" s="10"/>
       <c r="H93" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>54</v>
@@ -23010,21 +22788,21 @@
       <c r="G94" s="10"/>
       <c r="H94" s="10"/>
       <c r="I94" s="10" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>54</v>
@@ -23037,30 +22815,30 @@
       </c>
       <c r="G95" s="10"/>
       <c r="H95" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>74</v>
@@ -23068,21 +22846,21 @@
       <c r="G96" s="10"/>
       <c r="H96" s="10"/>
       <c r="I96" s="10" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>54</v>
@@ -23095,24 +22873,24 @@
       </c>
       <c r="G97" s="10"/>
       <c r="H97" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>54</v>
@@ -23126,21 +22904,21 @@
       <c r="G98" s="10"/>
       <c r="H98" s="10"/>
       <c r="I98" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>54</v>
@@ -23154,21 +22932,21 @@
       <c r="G99" s="10"/>
       <c r="H99" s="10"/>
       <c r="I99" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>54</v>
@@ -23181,24 +22959,24 @@
       </c>
       <c r="G100" s="10"/>
       <c r="H100" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>54</v>
@@ -23212,21 +22990,21 @@
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
       <c r="I101" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>54</v>
@@ -23240,10 +23018,10 @@
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
       <c r="I102" s="10" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
@@ -23258,19 +23036,19 @@
         <v>48</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="9"/>
       <c r="J103" s="9" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A104" s="11" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>103</v>
@@ -23289,18 +23067,18 @@
         <v>123</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" s="11" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>48</v>
@@ -23310,21 +23088,21 @@
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
       <c r="I105" s="11" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>54</v>
@@ -23338,21 +23116,21 @@
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
       <c r="I106" s="10" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>54</v>
@@ -23365,24 +23143,24 @@
       </c>
       <c r="G107" s="10"/>
       <c r="H107" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>54</v>
@@ -23396,21 +23174,21 @@
       <c r="G108" s="10"/>
       <c r="H108" s="10"/>
       <c r="I108" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>54</v>
@@ -23424,27 +23202,27 @@
       <c r="G109" s="10"/>
       <c r="H109" s="10"/>
       <c r="I109" s="10" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="F110" s="10" t="s">
         <v>74</v>
@@ -23452,21 +23230,21 @@
       <c r="G110" s="10"/>
       <c r="H110" s="10"/>
       <c r="I110" s="10" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>54</v>
@@ -23479,24 +23257,24 @@
       </c>
       <c r="G111" s="10"/>
       <c r="H111" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>48</v>
@@ -23506,21 +23284,21 @@
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
       <c r="I112" s="11" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>54</v>
@@ -23534,21 +23312,21 @@
       <c r="G113" s="10"/>
       <c r="H113" s="10"/>
       <c r="I113" s="10" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>54</v>
@@ -23561,24 +23339,24 @@
       </c>
       <c r="G114" s="10"/>
       <c r="H114" s="10" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>54</v>
@@ -23591,24 +23369,24 @@
       </c>
       <c r="G115" s="10"/>
       <c r="H115" s="10" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>54</v>
@@ -23622,21 +23400,21 @@
       <c r="G116" s="10"/>
       <c r="H116" s="10"/>
       <c r="I116" s="10" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>54</v>
@@ -23650,21 +23428,21 @@
       <c r="G117" s="10"/>
       <c r="H117" s="10"/>
       <c r="I117" s="10" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A118" s="11" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>48</v>
@@ -23674,21 +23452,21 @@
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
       <c r="I118" s="11" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>54</v>
@@ -23702,21 +23480,21 @@
       <c r="G119" s="10"/>
       <c r="H119" s="10"/>
       <c r="I119" s="10" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>54</v>
@@ -23730,10 +23508,10 @@
       <c r="G120" s="10"/>
       <c r="H120" s="10"/>
       <c r="I120" s="10" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.35">
@@ -23744,7 +23522,7 @@
         <v>70</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>54</v>
@@ -23760,13 +23538,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>54</v>
@@ -23782,13 +23560,13 @@
     </row>
     <row r="123" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>54</v>
@@ -23802,21 +23580,21 @@
       <c r="G123" s="10"/>
       <c r="H123" s="10"/>
       <c r="I123" s="10" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>54</v>
@@ -23829,24 +23607,24 @@
       </c>
       <c r="G124" s="10"/>
       <c r="H124" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A125" s="11" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D125" s="11" t="s">
         <v>48</v>
@@ -23856,21 +23634,21 @@
       <c r="G125" s="11"/>
       <c r="H125" s="11"/>
       <c r="I125" s="11" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>54</v>
@@ -23884,21 +23662,21 @@
       <c r="G126" s="10"/>
       <c r="H126" s="10"/>
       <c r="I126" s="10" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>54</v>
@@ -23912,10 +23690,10 @@
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
       <c r="I127" s="10" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.35">
@@ -23926,7 +23704,7 @@
         <v>70</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>54</v>
@@ -23942,13 +23720,13 @@
     </row>
     <row r="129" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="B129" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>54</v>
@@ -23962,21 +23740,21 @@
       <c r="G129" s="10"/>
       <c r="H129" s="10"/>
       <c r="I129" s="10" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B130" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>54</v>
@@ -23990,21 +23768,21 @@
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
       <c r="I130" s="10" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="B131" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>54</v>
@@ -24018,21 +23796,21 @@
       <c r="G131" s="10"/>
       <c r="H131" s="10"/>
       <c r="I131" s="10" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B132" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D132" s="10" t="s">
         <v>54</v>
@@ -24046,10 +23824,10 @@
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
       <c r="I132" s="10" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
     </row>
   </sheetData>

--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2DC3A7-25A8-4D0D-A0D6-C37B7AEEF3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBB4461-507D-4608-84A6-6E6509CFC584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="1306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="1307">
   <si>
     <t>CoreMeta4Cat Vocabulary Reference Workbook</t>
   </si>
@@ -4122,6 +4122,9 @@
   </si>
   <si>
     <t>A dimensionless physical quantity describing how effective a reactant is converted to the desired product in a chemical conversion. It is calculated as the ratio between the amount of the desired product and the amount of the desired product that could have been formed if all reactants were converted to the desired product. The selectivity is 1 (or 100 %) if no other than the desired product is formed.</t>
+  </si>
+  <si>
+    <t>Performance Descriptors</t>
   </si>
 </sst>
 </file>
@@ -18561,7 +18564,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118C8BAC-9B70-4E7A-BFF0-9A2BB55A4E4D}">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -18648,56 +18651,52 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>1291</v>
+        <v>1306</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="8" t="s">
-        <v>51</v>
-      </c>
+      <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8" t="s">
         <v>1292</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>1293</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="33" t="s">
+    <row r="6" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="33" t="s">
         <v>1294</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="27" t="s">
-        <v>1295</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="33" t="s">
-        <v>1297</v>
-      </c>
       <c r="B6" s="30" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C6" s="34" t="s">
         <v>1291</v>
@@ -18707,19 +18706,19 @@
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="35" t="s">
-        <v>1298</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="I6" s="27" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>1291</v>
@@ -18729,46 +18728,56 @@
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
       <c r="H7" s="30"/>
-      <c r="I7" s="27" t="s">
-        <v>1301</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A8" s="37" t="s">
-        <v>1303</v>
+      <c r="I7" s="35" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="33" t="s">
+        <v>1300</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>1291</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="35" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="27" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A9" s="37" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="35" t="s">
         <v>1304</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J9" s="36" t="s">
         <v>1305</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8"/>
@@ -18794,37 +18803,21 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
         <v>852</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>855</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>70</v>
@@ -18834,7 +18827,7 @@
         <v>51</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>74</v>
@@ -18844,15 +18837,15 @@
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>70</v>
@@ -18862,223 +18855,227 @@
         <v>51</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8" t="s">
         <v>859</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J15" s="8" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+    <row r="16" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
         <v>861</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="B16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10" t="s">
+      <c r="F16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10" t="s">
         <v>862</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J16" s="10" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
+    <row r="17" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B17" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>861</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11" t="s">
+      <c r="D17" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J17" s="11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+    <row r="18" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
         <v>864</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9" t="s">
+      <c r="B18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E18" s="9" t="s">
         <v>865</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9" t="s">
+      <c r="F18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9" t="s">
         <v>866</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J18" s="9" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="174" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+    <row r="19" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
         <v>865</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B19" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>864</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11" t="s">
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J19" s="11" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
+    <row r="20" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
         <v>869</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
-        <v>870</v>
-      </c>
       <c r="B20" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>869</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="H20" s="9"/>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9" t="s">
         <v>872</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J21" s="9" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
+    <row r="22" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
         <v>874</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B22" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>870</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11" t="s">
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11" t="s">
         <v>875</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J22" s="11" t="s">
         <v>876</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="13" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>874</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="20" t="s">
-        <v>1221</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>70</v>
@@ -19094,61 +19091,63 @@
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="I23" s="20" t="s">
+        <v>1221</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="13" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>874</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="20" t="s">
         <v>1222</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J24" s="15" t="s">
         <v>1220</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A24" s="21" t="s">
+    <row r="25" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A25" s="21" t="s">
         <v>1227</v>
       </c>
-      <c r="B24" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="22" t="s">
+      <c r="B25" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="22" t="s">
         <v>874</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D25" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22" t="s">
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22" t="s">
         <v>1224</v>
       </c>
-      <c r="J24" s="23" t="s">
+      <c r="J25" s="23" t="s">
         <v>1225</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
+    <row r="26" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
         <v>1232</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11" t="s">
-        <v>1235</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
-        <v>1234</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>103</v>
@@ -19161,106 +19160,104 @@
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="24" t="s">
+      <c r="I26" s="11" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="24" t="s">
         <v>1230</v>
       </c>
-      <c r="B27" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="25" t="s">
+      <c r="B28" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="25" t="s">
         <v>874</v>
       </c>
-      <c r="D27" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25" t="s">
+      <c r="D28" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25" t="s">
         <v>1231</v>
       </c>
-      <c r="J27" s="26" t="s">
+      <c r="J28" s="26" t="s">
         <v>1226</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="24" t="s">
+    <row r="29" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="24" t="s">
         <v>1236</v>
       </c>
-      <c r="B28" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="24" t="s">
+      <c r="B29" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="24" t="s">
         <v>874</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D29" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24" t="s">
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24" t="s">
         <v>1237</v>
       </c>
-      <c r="J28" s="24" t="s">
+      <c r="J29" s="24" t="s">
         <v>1238</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
+    <row r="30" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
         <v>877</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B30" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>870</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11" t="s">
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11" t="s">
         <v>878</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J30" s="11" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
+    <row r="31" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="13" t="s">
         <v>1243</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>877</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13" t="s">
-        <v>1244</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
-        <v>1246</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>70</v>
@@ -19275,56 +19272,60 @@
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
+      <c r="I31" s="13" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>1245</v>
+      </c>
     </row>
     <row r="32" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="13" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>877</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="33" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="21" t="s">
         <v>1240</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="21" t="s">
+      <c r="B33" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>877</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D33" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21" t="s">
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21" t="s">
         <v>1241</v>
       </c>
-      <c r="J32" s="21" t="s">
+      <c r="J33" s="21" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="24" t="s">
+    <row r="34" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="24" t="s">
         <v>1239</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>877</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="31"/>
-    </row>
-    <row r="34" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A34" s="25" t="s">
-        <v>232</v>
       </c>
       <c r="B34" s="25" t="s">
         <v>70</v>
@@ -19339,16 +19340,12 @@
       <c r="F34" s="25"/>
       <c r="G34" s="25"/>
       <c r="H34" s="25"/>
-      <c r="I34" s="25" t="s">
-        <v>1248</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="I34" s="30"/>
+      <c r="J34" s="31"/>
+    </row>
+    <row r="35" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A35" s="25" t="s">
-        <v>1247</v>
+        <v>232</v>
       </c>
       <c r="B35" s="25" t="s">
         <v>70</v>
@@ -19356,65 +19353,69 @@
       <c r="C35" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="D35" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
+      <c r="D35" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
       <c r="I35" s="25" t="s">
+        <v>1248</v>
+      </c>
+      <c r="J35" s="25" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="25" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>877</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="25" t="s">
         <v>1249</v>
       </c>
-      <c r="J35" s="25" t="s">
+      <c r="J36" s="25" t="s">
         <v>1251</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="11" t="s">
+    <row r="37" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
         <v>880</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B37" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C37" s="11" t="s">
         <v>870</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11" t="s">
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11" t="s">
         <v>881</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="J37" s="11" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="13" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
     </row>
     <row r="38" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>70</v>
@@ -19433,28 +19434,28 @@
       <c r="J38" s="13"/>
     </row>
     <row r="39" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="21" t="s">
-        <v>1254</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="21" t="s">
+      <c r="A39" s="13" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>880</v>
       </c>
-      <c r="D39" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
+      <c r="D39" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
     </row>
     <row r="40" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="21" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="B40" s="21" t="s">
         <v>70</v>
@@ -19474,7 +19475,7 @@
     </row>
     <row r="41" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="21" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B41" s="21" t="s">
         <v>70</v>
@@ -19492,9 +19493,9 @@
       <c r="I41" s="21"/>
       <c r="J41" s="21"/>
     </row>
-    <row r="42" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="B42" s="21" t="s">
         <v>70</v>
@@ -19509,58 +19510,58 @@
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="21"/>
-      <c r="I42" s="21" t="s">
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+    </row>
+    <row r="43" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A43" s="21" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>880</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21" t="s">
         <v>1256</v>
       </c>
-      <c r="J42" s="21" t="s">
+      <c r="J43" s="21" t="s">
         <v>1257</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A43" s="11" t="s">
+    <row r="44" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
         <v>883</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B44" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C44" s="11" t="s">
         <v>870</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11" t="s">
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11" t="s">
         <v>884</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="J44" s="11" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="13" t="s">
+    <row r="45" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="13" t="s">
         <v>1260</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>883</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-    </row>
-    <row r="45" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="13" t="s">
-        <v>1261</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>70</v>
@@ -19575,16 +19576,12 @@
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
-      <c r="I45" s="13" t="s">
-        <v>1262</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="13" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>70</v>
@@ -19599,12 +19596,16 @@
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
+      <c r="I46" s="13" t="s">
+        <v>1262</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>1263</v>
+      </c>
     </row>
     <row r="47" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="13" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>70</v>
@@ -19619,82 +19620,82 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
-      <c r="I47" s="13" t="s">
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="13" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>883</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13" t="s">
         <v>1265</v>
       </c>
-      <c r="J47" s="13" t="s">
+      <c r="J48" s="13" t="s">
         <v>1266</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="21" t="s">
+    <row r="49" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="21" t="s">
         <v>1268</v>
       </c>
-      <c r="B48" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>883</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
-    </row>
-    <row r="49" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="32" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="21" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>883</v>
       </c>
-      <c r="D49" s="32" t="s">
+      <c r="D49" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
     </row>
     <row r="50" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="32" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>883</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+    </row>
+    <row r="51" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
         <v>133</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J50" s="11"/>
-    </row>
-    <row r="51" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
-        <v>886</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>870</v>
+        <v>1269</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
@@ -19702,59 +19703,59 @@
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
       <c r="I51" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J51" s="11"/>
+    </row>
+    <row r="52" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="11" t="s">
+        <v>886</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11" t="s">
         <v>887</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J52" s="11" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A52" s="13" t="s">
+    <row r="53" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A53" s="13" t="s">
         <v>1255</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="13" t="s">
+      <c r="B53" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D53" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13" t="s">
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13" t="s">
         <v>1256</v>
       </c>
-      <c r="J52" s="13" t="s">
+      <c r="J53" s="13" t="s">
         <v>1257</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="32" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B53" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="32" t="s">
-        <v>886</v>
-      </c>
-      <c r="D53" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
     </row>
     <row r="54" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="32" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B54" s="32" t="s">
         <v>70</v>
@@ -19774,7 +19775,7 @@
     </row>
     <row r="55" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="32" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B55" s="32" t="s">
         <v>70</v>
@@ -19794,7 +19795,7 @@
     </row>
     <row r="56" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="32" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B56" s="32" t="s">
         <v>70</v>
@@ -19812,51 +19813,51 @@
       <c r="I56" s="32"/>
       <c r="J56" s="32"/>
     </row>
-    <row r="57" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="11" t="s">
+    <row r="57" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="32" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>886</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+    </row>
+    <row r="58" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="11" t="s">
         <v>889</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B58" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C58" s="11" t="s">
         <v>870</v>
       </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11" t="s">
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11" t="s">
         <v>890</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="J58" s="11" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="13" t="s">
-        <v>1276</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>889</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
     </row>
     <row r="59" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="13" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>70</v>
@@ -19876,7 +19877,7 @@
     </row>
     <row r="60" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="13" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>70</v>
@@ -19894,55 +19895,51 @@
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
     </row>
-    <row r="61" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="11" t="s">
+    <row r="61" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="13" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>889</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+    </row>
+    <row r="62" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="11" t="s">
         <v>892</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B62" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>870</v>
       </c>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11" t="s">
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11" t="s">
         <v>893</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="J62" s="11" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="62" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A62" s="32" t="s">
+    <row r="63" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A63" s="32" t="s">
         <v>1255</v>
-      </c>
-      <c r="B62" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="32" t="s">
-        <v>892</v>
-      </c>
-      <c r="D62" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32" t="s">
-        <v>1256</v>
-      </c>
-      <c r="J62" s="32" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="32" t="s">
-        <v>1286</v>
       </c>
       <c r="B63" s="32" t="s">
         <v>70</v>
@@ -19957,12 +19954,16 @@
       <c r="F63" s="32"/>
       <c r="G63" s="32"/>
       <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="32"/>
-    </row>
-    <row r="64" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="I63" s="32" t="s">
+        <v>1256</v>
+      </c>
+      <c r="J63" s="32" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="32" t="s">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>70</v>
@@ -19977,16 +19978,12 @@
       <c r="F64" s="32"/>
       <c r="G64" s="32"/>
       <c r="H64" s="32"/>
-      <c r="I64" s="32" t="s">
-        <v>1278</v>
-      </c>
-      <c r="J64" s="32" t="s">
-        <v>1279</v>
-      </c>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
     </row>
     <row r="65" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="32" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="B65" s="32" t="s">
         <v>70</v>
@@ -19995,22 +19992,22 @@
         <v>892</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E65" s="32"/>
       <c r="F65" s="32"/>
       <c r="G65" s="32"/>
       <c r="H65" s="32"/>
       <c r="I65" s="32" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="J65" s="32" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="32" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="B66" s="32" t="s">
         <v>70</v>
@@ -20026,65 +20023,61 @@
       <c r="G66" s="32"/>
       <c r="H66" s="32"/>
       <c r="I66" s="32" t="s">
+        <v>1281</v>
+      </c>
+      <c r="J66" s="32" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="32" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B67" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>892</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32" t="s">
         <v>1284</v>
       </c>
-      <c r="J66" s="32" t="s">
+      <c r="J67" s="32" t="s">
         <v>1285</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="11" t="s">
+    <row r="68" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="11" t="s">
         <v>895</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B68" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C68" s="11" t="s">
         <v>870</v>
       </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11" t="s">
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11" t="s">
         <v>896</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="J68" s="11" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A68" s="10" t="s">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="10" t="s">
         <v>898</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>895</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10" t="s">
-        <v>899</v>
-      </c>
-      <c r="J68" s="10" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A69" s="10" t="s">
-        <v>901</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>70</v>
@@ -20096,25 +20089,23 @@
         <v>54</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G69" s="10"/>
-      <c r="H69" s="10" t="s">
-        <v>682</v>
-      </c>
+      <c r="H69" s="10"/>
       <c r="I69" s="10" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>70</v>
@@ -20126,34 +20117,64 @@
         <v>54</v>
       </c>
       <c r="E70" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G70" s="10"/>
+      <c r="H70" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>902</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10" t="s">
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="J70" s="10" t="s">
+      <c r="J71" s="10" t="s">
         <v>906</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I22" r:id="rId1" display="voc4cat:0007254" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
-    <hyperlink ref="I23" r:id="rId2" display="voc4cat:0007255" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
-    <hyperlink ref="I27" r:id="rId3" display="voc4cat:0007258" xr:uid="{ECE0B83D-4C10-4937-A571-CB1A78F8D921}"/>
-    <hyperlink ref="I25" r:id="rId4" display="voc4cat:0007256" xr:uid="{B8B87E67-D090-44FF-99F3-C73E22B0384A}"/>
-    <hyperlink ref="I28" r:id="rId5" xr:uid="{AD38AF27-1671-4048-B637-B5B450D15DAD}"/>
-    <hyperlink ref="I34" r:id="rId6" xr:uid="{361B543E-C568-4568-8088-6E70DE9F3B27}"/>
-    <hyperlink ref="I35" r:id="rId7" xr:uid="{1719255A-01AA-4404-94C6-32789CDF8402}"/>
-    <hyperlink ref="I64" r:id="rId8" xr:uid="{67C09C0D-2279-4237-A447-58639A2AE5CC}"/>
+    <hyperlink ref="I23" r:id="rId1" display="voc4cat:0007254" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
+    <hyperlink ref="I24" r:id="rId2" display="voc4cat:0007255" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
+    <hyperlink ref="I28" r:id="rId3" display="voc4cat:0007258" xr:uid="{ECE0B83D-4C10-4937-A571-CB1A78F8D921}"/>
+    <hyperlink ref="I26" r:id="rId4" display="voc4cat:0007256" xr:uid="{B8B87E67-D090-44FF-99F3-C73E22B0384A}"/>
+    <hyperlink ref="I29" r:id="rId5" xr:uid="{AD38AF27-1671-4048-B637-B5B450D15DAD}"/>
+    <hyperlink ref="I35" r:id="rId6" xr:uid="{361B543E-C568-4568-8088-6E70DE9F3B27}"/>
+    <hyperlink ref="I36" r:id="rId7" xr:uid="{1719255A-01AA-4404-94C6-32789CDF8402}"/>
+    <hyperlink ref="I65" r:id="rId8" xr:uid="{67C09C0D-2279-4237-A447-58639A2AE5CC}"/>
     <hyperlink ref="I2" r:id="rId9" xr:uid="{EE99F099-E6BA-477F-A260-88529C3F7434}"/>
-    <hyperlink ref="I4" r:id="rId10" xr:uid="{BDA420BA-A173-4F89-A841-856E53112396}"/>
-    <hyperlink ref="I8" r:id="rId11" xr:uid="{54581B7D-9C1E-4C15-887D-BA48A1859B95}"/>
-    <hyperlink ref="I7" r:id="rId12" xr:uid="{46577A97-6DF9-402F-BCAD-57196F467970}"/>
-    <hyperlink ref="I6" r:id="rId13" xr:uid="{11743F2A-1294-4AA1-9B68-D52B44449D93}"/>
-    <hyperlink ref="I5" r:id="rId14" xr:uid="{336B9A92-59C1-445E-9AD3-47037654015F}"/>
+    <hyperlink ref="I5" r:id="rId10" xr:uid="{BDA420BA-A173-4F89-A841-856E53112396}"/>
+    <hyperlink ref="I9" r:id="rId11" xr:uid="{54581B7D-9C1E-4C15-887D-BA48A1859B95}"/>
+    <hyperlink ref="I8" r:id="rId12" xr:uid="{46577A97-6DF9-402F-BCAD-57196F467970}"/>
+    <hyperlink ref="I7" r:id="rId13" xr:uid="{11743F2A-1294-4AA1-9B68-D52B44449D93}"/>
+    <hyperlink ref="I6" r:id="rId14" xr:uid="{336B9A92-59C1-445E-9AD3-47037654015F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBB4461-507D-4608-84A6-6E6509CFC584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16662913-CC0C-4A12-9728-42CAAC91ACDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5188" uniqueCount="1307">
   <si>
     <t>CoreMeta4Cat Vocabulary Reference Workbook</t>
   </si>
@@ -18659,8 +18659,12 @@
         <v>70</v>
       </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1291</v>
+      </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>

--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16662913-CC0C-4A12-9728-42CAAC91ACDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078E6B55-3503-4D2A-B036-AD54C04FABC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18663,7 +18663,7 @@
         <v>51</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1291</v>
+        <v>1306</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>

--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078E6B55-3503-4D2A-B036-AD54C04FABC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF44EAD-6563-4DC8-8084-2F1E68B027B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5188" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5190" uniqueCount="1307">
   <si>
     <t>CoreMeta4Cat Vocabulary Reference Workbook</t>
   </si>
@@ -4423,16 +4423,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4489,6 +4479,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4800,17 +4800,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="36"/>
     </row>
     <row r="4" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="8" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="17"/>
+      <c r="B9" s="36"/>
     </row>
     <row r="10" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -4909,10 +4909,10 @@
     </row>
     <row r="17" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="17"/>
+      <c r="B18" s="36"/>
     </row>
     <row r="19" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -5016,19 +5016,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
     </row>
     <row r="2" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -5065,11 +5065,11 @@
     </row>
     <row r="7" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
     </row>
     <row r="9" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -5153,18 +5153,18 @@
     </row>
     <row r="19" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
     </row>
     <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -18576,7 +18576,7 @@
     <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
     <col min="9" max="9" width="46" customWidth="1"/>
-    <col min="10" max="10" width="60" customWidth="1"/>
+    <col min="10" max="10" width="102.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -18663,10 +18663,14 @@
         <v>51</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1306</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+        <v>1291</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -18696,90 +18700,90 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="29" t="s">
         <v>1294</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="34" t="s">
+      <c r="B6" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>1291</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="27" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="23" t="s">
         <v>1295</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="24" t="s">
         <v>1296</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="29" t="s">
         <v>1297</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>1291</v>
       </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="35" t="s">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="31" t="s">
         <v>1298</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="32" t="s">
         <v>1299</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="29" t="s">
         <v>1300</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="34" t="s">
+      <c r="B8" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>1291</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="27" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="23" t="s">
         <v>1301</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="24" t="s">
         <v>1302</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="33" t="s">
         <v>1303</v>
       </c>
-      <c r="B9" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="34" t="s">
+      <c r="B9" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>1291</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="35" t="s">
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="31" t="s">
         <v>1304</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="32" t="s">
         <v>1305</v>
       </c>
     </row>
@@ -19031,7 +19035,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="145" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>870</v>
       </c>
@@ -19055,7 +19059,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>874</v>
       </c>
@@ -19077,7 +19081,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
         <v>1228</v>
       </c>
@@ -19094,14 +19098,14 @@
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="16" t="s">
         <v>1221</v>
       </c>
       <c r="J23" s="15" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>1229</v>
       </c>
@@ -19118,38 +19122,38 @@
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="16" t="s">
         <v>1222</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>1220</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A25" s="21" t="s">
+    <row r="25" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="17" t="s">
         <v>1227</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="22" t="s">
+      <c r="B25" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="18" t="s">
         <v>874</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22" t="s">
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18" t="s">
         <v>1224</v>
       </c>
-      <c r="J25" s="23" t="s">
+      <c r="J25" s="19" t="s">
         <v>1225</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
         <v>1232</v>
       </c>
@@ -19189,55 +19193,55 @@
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="24" t="s">
+    <row r="28" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="20" t="s">
         <v>1230</v>
       </c>
-      <c r="B28" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="25" t="s">
+      <c r="B28" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>874</v>
       </c>
-      <c r="D28" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25" t="s">
+      <c r="D28" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21" t="s">
         <v>1231</v>
       </c>
-      <c r="J28" s="26" t="s">
+      <c r="J28" s="22" t="s">
         <v>1226</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="24" t="s">
+    <row r="29" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="20" t="s">
         <v>1236</v>
       </c>
-      <c r="B29" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="24" t="s">
+      <c r="B29" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="20" t="s">
         <v>874</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24" t="s">
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20" t="s">
         <v>1237</v>
       </c>
-      <c r="J29" s="24" t="s">
+      <c r="J29" s="20" t="s">
         <v>1238</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>877</v>
       </c>
@@ -19304,98 +19308,98 @@
       <c r="J32" s="13"/>
     </row>
     <row r="33" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="17" t="s">
         <v>1240</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="21" t="s">
+      <c r="B33" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>877</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21" t="s">
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17" t="s">
         <v>1241</v>
       </c>
-      <c r="J33" s="21" t="s">
+      <c r="J33" s="17" t="s">
         <v>1242</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="20" t="s">
         <v>1239</v>
       </c>
-      <c r="B34" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="25" t="s">
+      <c r="B34" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>877</v>
       </c>
-      <c r="D34" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="31"/>
-    </row>
-    <row r="35" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A35" s="25" t="s">
+      <c r="D34" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="27"/>
+    </row>
+    <row r="35" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="B35" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="25" t="s">
+      <c r="B35" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>877</v>
       </c>
-      <c r="D35" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25" t="s">
+      <c r="D35" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21" t="s">
         <v>1248</v>
       </c>
-      <c r="J35" s="25" t="s">
+      <c r="J35" s="21" t="s">
         <v>1250</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="25" t="s">
+    <row r="36" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="21" t="s">
         <v>1247</v>
       </c>
-      <c r="B36" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="25" t="s">
+      <c r="B36" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>877</v>
       </c>
-      <c r="D36" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="25" t="s">
+      <c r="D36" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="21" t="s">
         <v>1249</v>
       </c>
-      <c r="J36" s="25" t="s">
+      <c r="J36" s="21" t="s">
         <v>1251</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
         <v>880</v>
       </c>
@@ -19458,86 +19462,86 @@
       <c r="J39" s="13"/>
     </row>
     <row r="40" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="17" t="s">
         <v>1254</v>
       </c>
-      <c r="B40" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="21" t="s">
+      <c r="B40" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="17" t="s">
         <v>880</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
     </row>
     <row r="41" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="17" t="s">
         <v>1258</v>
       </c>
-      <c r="B41" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="21" t="s">
+      <c r="B41" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>880</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D41" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
     </row>
     <row r="42" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="17" t="s">
         <v>1259</v>
       </c>
-      <c r="B42" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="21" t="s">
+      <c r="B42" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="17" t="s">
         <v>880</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-    </row>
-    <row r="43" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A43" s="21" t="s">
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+    </row>
+    <row r="43" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" s="17" t="s">
         <v>1255</v>
       </c>
-      <c r="B43" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="21" t="s">
+      <c r="B43" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>880</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21" t="s">
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17" t="s">
         <v>1256</v>
       </c>
-      <c r="J43" s="21" t="s">
+      <c r="J43" s="17" t="s">
         <v>1257</v>
       </c>
     </row>
@@ -19583,7 +19587,7 @@
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
     </row>
-    <row r="46" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="13" t="s">
         <v>1261</v>
       </c>
@@ -19652,44 +19656,44 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="17" t="s">
         <v>1268</v>
       </c>
-      <c r="B49" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="21" t="s">
+      <c r="B49" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="17" t="s">
         <v>883</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
     </row>
     <row r="50" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="28" t="s">
         <v>1269</v>
       </c>
-      <c r="B50" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="21" t="s">
+      <c r="B50" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="17" t="s">
         <v>883</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
     </row>
     <row r="51" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
@@ -19711,7 +19715,7 @@
       </c>
       <c r="J51" s="11"/>
     </row>
-    <row r="52" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
         <v>886</v>
       </c>
@@ -19733,7 +19737,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="13" t="s">
         <v>1255</v>
       </c>
@@ -19758,86 +19762,86 @@
       </c>
     </row>
     <row r="54" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="32" t="s">
+      <c r="A54" s="28" t="s">
         <v>1270</v>
       </c>
-      <c r="B54" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" s="32" t="s">
+      <c r="B54" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="28" t="s">
         <v>886</v>
       </c>
-      <c r="D54" s="32" t="s">
+      <c r="D54" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
     </row>
     <row r="55" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="32" t="s">
+      <c r="A55" s="28" t="s">
         <v>1271</v>
       </c>
-      <c r="B55" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="32" t="s">
+      <c r="B55" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="28" t="s">
         <v>886</v>
       </c>
-      <c r="D55" s="32" t="s">
+      <c r="D55" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
     </row>
     <row r="56" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="32" t="s">
+      <c r="A56" s="28" t="s">
         <v>1272</v>
       </c>
-      <c r="B56" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="32" t="s">
+      <c r="B56" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="28" t="s">
         <v>886</v>
       </c>
-      <c r="D56" s="32" t="s">
+      <c r="D56" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="32"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
     </row>
     <row r="57" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="32" t="s">
+      <c r="A57" s="28" t="s">
         <v>1273</v>
       </c>
-      <c r="B57" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" s="32" t="s">
+      <c r="B57" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" s="28" t="s">
         <v>886</v>
       </c>
-      <c r="D57" s="32" t="s">
+      <c r="D57" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="32"/>
-    </row>
-    <row r="58" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+    </row>
+    <row r="58" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="11" t="s">
         <v>889</v>
       </c>
@@ -19919,7 +19923,7 @@
       <c r="I61" s="13"/>
       <c r="J61" s="13"/>
     </row>
-    <row r="62" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="11" t="s">
         <v>892</v>
       </c>
@@ -19941,123 +19945,123 @@
         <v>894</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A63" s="32" t="s">
+    <row r="63" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="28" t="s">
         <v>1255</v>
       </c>
-      <c r="B63" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="32" t="s">
+      <c r="B63" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="28" t="s">
         <v>892</v>
       </c>
-      <c r="D63" s="32" t="s">
+      <c r="D63" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32" t="s">
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28" t="s">
         <v>1256</v>
       </c>
-      <c r="J63" s="32" t="s">
+      <c r="J63" s="28" t="s">
         <v>1257</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="28" t="s">
         <v>1286</v>
       </c>
-      <c r="B64" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="32" t="s">
+      <c r="B64" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="28" t="s">
         <v>892</v>
       </c>
-      <c r="D64" s="32" t="s">
+      <c r="D64" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="32"/>
-    </row>
-    <row r="65" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A65" s="32" t="s">
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+    </row>
+    <row r="65" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="28" t="s">
         <v>1277</v>
       </c>
-      <c r="B65" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="32" t="s">
+      <c r="B65" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="28" t="s">
         <v>892</v>
       </c>
-      <c r="D65" s="32" t="s">
+      <c r="D65" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32" t="s">
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="28"/>
+      <c r="I65" s="28" t="s">
         <v>1278</v>
       </c>
-      <c r="J65" s="32" t="s">
+      <c r="J65" s="28" t="s">
         <v>1279</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A66" s="32" t="s">
+      <c r="A66" s="28" t="s">
         <v>1280</v>
       </c>
-      <c r="B66" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" s="32" t="s">
+      <c r="B66" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="28" t="s">
         <v>892</v>
       </c>
-      <c r="D66" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="32" t="s">
+      <c r="D66" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="28"/>
+      <c r="I66" s="28" t="s">
         <v>1281</v>
       </c>
-      <c r="J66" s="32" t="s">
+      <c r="J66" s="28" t="s">
         <v>1282</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="32" t="s">
+    <row r="67" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="28" t="s">
         <v>1283</v>
       </c>
-      <c r="B67" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="32" t="s">
+      <c r="B67" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C67" s="28" t="s">
         <v>892</v>
       </c>
-      <c r="D67" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="E67" s="32"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="32" t="s">
+      <c r="D67" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28" t="s">
         <v>1284</v>
       </c>
-      <c r="J67" s="32" t="s">
+      <c r="J67" s="28" t="s">
         <v>1285</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="11" t="s">
         <v>895</v>
       </c>
@@ -20107,7 +20111,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>901</v>
       </c>
@@ -20137,7 +20141,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="10" t="s">
         <v>904</v>
       </c>

--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF44EAD-6563-4DC8-8084-2F1E68B027B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9259E7EA-5FC8-4E91-ABD3-4D232EE003BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-75" windowWidth="25440" windowHeight="15270" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31830" yWindow="3090" windowWidth="25170" windowHeight="15000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5190" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5195" uniqueCount="1315">
   <si>
     <t>CoreMeta4Cat Vocabulary Reference Workbook</t>
   </si>
@@ -2678,17 +2678,6 @@
   <si>
     <t>Type of catalyst used (e.g. heterogeneous, homogeneous, biocatalyst).
 For heterogeneous catalysts, use voc4cat terms where available.</t>
-  </si>
-  <si>
-    <t>feed composition range</t>
-  </si>
-  <si>
-    <t>coremeta4cat:feed_composition_range</t>
-  </si>
-  <si>
-    <t>Feed composition range studied, provided as a QuantitativeRange.
-Express concentration bounds in an appropriate unit (e.g. "mol/L", "%" for
-vol% or mol%). For fixed-composition experiments use reactant.has_concentration.</t>
   </si>
   <si>
     <t>product identification method</t>
@@ -4125,6 +4114,39 @@
   </si>
   <si>
     <t>Performance Descriptors</t>
+  </si>
+  <si>
+    <t>heterogeneous catalysis</t>
+  </si>
+  <si>
+    <t>voc4cat:0007003</t>
+  </si>
+  <si>
+    <t>A substance that increases the rate of a chemical reaction that is in a different phase than the reagents.</t>
+  </si>
+  <si>
+    <t>electrocatalyst</t>
+  </si>
+  <si>
+    <t>A material which directs and accelerates an electrochemical reaction while remaining unchanged in the process.</t>
+  </si>
+  <si>
+    <t>voc4cat:0000254</t>
+  </si>
+  <si>
+    <t>biocatalyst</t>
+  </si>
+  <si>
+    <t>coremeta4cat:biocatalyst</t>
+  </si>
+  <si>
+    <t>homogeneous catalyst</t>
+  </si>
+  <si>
+    <t>coremeta4cat:homogeneous_catalyst</t>
+  </si>
+  <si>
+    <t>A substance that increases the rate of a chemical reaction that is in the phase as the reagents.</t>
   </si>
 </sst>
 </file>
@@ -4174,7 +4196,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4244,8 +4266,32 @@
         <bgColor theme="4" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -4374,11 +4420,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -4462,9 +4532,6 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4474,12 +4541,10 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -4489,6 +4554,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4800,17 +4895,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
+      <c r="B1" s="35"/>
     </row>
     <row r="2" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="35"/>
     </row>
     <row r="4" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -4846,10 +4941,10 @@
     </row>
     <row r="8" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="36"/>
+      <c r="B9" s="35"/>
     </row>
     <row r="10" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -4909,10 +5004,10 @@
     </row>
     <row r="17" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="36"/>
+      <c r="B18" s="35"/>
     </row>
     <row r="19" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -5016,19 +5111,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -5065,11 +5160,11 @@
     </row>
     <row r="7" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
     </row>
     <row r="9" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -5153,18 +5248,18 @@
     </row>
     <row r="19" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
     </row>
     <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -18564,7 +18659,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118C8BAC-9B70-4E7A-BFF0-9A2BB55A4E4D}">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -18612,8 +18707,8 @@
       </c>
     </row>
     <row r="2" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>1288</v>
+      <c r="A2" s="38" t="s">
+        <v>1285</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>70</v>
@@ -18627,15 +18722,15 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>1287</v>
+      <c r="A3" s="38" t="s">
+        <v>1284</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>70</v>
@@ -18652,8 +18747,8 @@
       <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>1306</v>
+      <c r="A4" s="38" t="s">
+        <v>1303</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>70</v>
@@ -18663,7 +18758,7 @@
         <v>51</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>74</v>
@@ -18676,14 +18771,14 @@
       <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>1291</v>
+      <c r="A5" s="38" t="s">
+        <v>1288</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>51</v>
@@ -18693,21 +18788,21 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="s">
-        <v>1294</v>
+      <c r="A6" s="39" t="s">
+        <v>1291</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="30" t="s">
-        <v>1291</v>
+      <c r="C6" s="29" t="s">
+        <v>1288</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
@@ -18715,43 +18810,43 @@
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
       <c r="I6" s="23" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
-        <v>1297</v>
+      <c r="A7" s="39" t="s">
+        <v>1294</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="30" t="s">
-        <v>1291</v>
+      <c r="C7" s="29" t="s">
+        <v>1288</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
-      <c r="I7" s="31" t="s">
-        <v>1298</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>1299</v>
+      <c r="I7" s="30" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>1296</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
-        <v>1300</v>
+      <c r="A8" s="39" t="s">
+        <v>1297</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="30" t="s">
-        <v>1291</v>
+      <c r="C8" s="29" t="s">
+        <v>1288</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
@@ -18759,337 +18854,359 @@
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
       <c r="I8" s="23" t="s">
+        <v>1298</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A9" s="40" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="30" t="s">
         <v>1301</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J9" s="31" t="s">
         <v>1302</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A9" s="33" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>1291</v>
-      </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="31" t="s">
-        <v>1304</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="D10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="I10" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="D11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="I11" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="D12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>852</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8" t="s">
-        <v>856</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="I12" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="46" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="41" t="s">
         <v>858</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8" t="s">
-        <v>859</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="42" t="s">
+        <v>1305</v>
+      </c>
+      <c r="J13" s="43" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="46" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>858</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41" t="s">
+        <v>1309</v>
+      </c>
+      <c r="J14" s="41" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="47" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>858</v>
+      </c>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="44" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J15" s="45"/>
+    </row>
+    <row r="16" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="47" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>858</v>
+      </c>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="44" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
         <v>861</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10" t="s">
+      <c r="B17" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="F17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="J17" s="9" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>861</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>864</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>865</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9" t="s">
+    </row>
+    <row r="19" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
         <v>866</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="B19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>867</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="174" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
-        <v>865</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="F19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>864</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
-        <v>869</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="9" t="s">
+        <v>866</v>
+      </c>
       <c r="D20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>870</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9" t="s">
+    </row>
+    <row r="21" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
         <v>871</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="145" x14ac:dyDescent="0.35">
-      <c r="A21" s="9" t="s">
-        <v>870</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>869</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="C21" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="13" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>871</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>874</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11" t="s">
-        <v>875</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>876</v>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="16" t="s">
+        <v>1218</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>1216</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>48</v>
@@ -19099,171 +19216,171 @@
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="I23" s="16" t="s">
+        <v>1219</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="17" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>871</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18" t="s">
         <v>1221</v>
       </c>
-      <c r="J23" s="15" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="13" t="s">
+      <c r="J24" s="19" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
         <v>1229</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>874</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="16" t="s">
-        <v>1222</v>
-      </c>
-      <c r="J24" s="15" t="s">
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>1220</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="17" t="s">
-        <v>1227</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>874</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11" t="s">
+        <v>1232</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="20" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>871</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21" t="s">
+        <v>1228</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="20" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>871</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J28" s="20" t="s">
         <v>1235</v>
       </c>
-      <c r="J26" s="11" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B27" s="11" t="s">
+    </row>
+    <row r="29" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>874</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="20" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="21" t="s">
+      <c r="C29" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="13" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>874</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21" t="s">
-        <v>1231</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="20" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>874</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20" t="s">
-        <v>1237</v>
-      </c>
-      <c r="J29" s="20" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
-        <v>877</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11" t="s">
-        <v>878</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="D30" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13" t="s">
+        <v>1241</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="13" t="s">
         <v>1243</v>
       </c>
@@ -19271,7 +19388,7 @@
         <v>70</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>48</v>
@@ -19280,66 +19397,62 @@
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
-      <c r="I31" s="13" t="s">
-        <v>1244</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>1245</v>
-      </c>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="13" t="s">
-        <v>1246</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>877</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
+      <c r="A32" s="17" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>874</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>1239</v>
+      </c>
     </row>
     <row r="33" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="17" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>877</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17" t="s">
-        <v>1241</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="20" t="s">
-        <v>1239</v>
+      <c r="A33" s="20" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>874</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="27"/>
+    </row>
+    <row r="34" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="21" t="s">
+        <v>232</v>
       </c>
       <c r="B34" s="21" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D34" s="21" t="s">
         <v>54</v>
@@ -19348,88 +19461,88 @@
       <c r="F34" s="21"/>
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="27"/>
+      <c r="I34" s="21" t="s">
+        <v>1245</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>1247</v>
+      </c>
     </row>
     <row r="35" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
-        <v>232</v>
+        <v>1244</v>
       </c>
       <c r="B35" s="21" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="21" t="s">
+        <v>874</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="21" t="s">
+        <v>1246</v>
+      </c>
+      <c r="J35" s="21" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
         <v>877</v>
       </c>
-      <c r="D35" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21" t="s">
-        <v>1248</v>
-      </c>
-      <c r="J35" s="21" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="21" t="s">
-        <v>1247</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="21" t="s">
+      <c r="B36" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="13" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>877</v>
       </c>
-      <c r="D36" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="21" t="s">
-        <v>1249</v>
-      </c>
-      <c r="J36" s="21" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="11" t="s">
-        <v>880</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11" t="s">
-        <v>881</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>882</v>
-      </c>
+      <c r="D37" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>48</v>
@@ -19442,34 +19555,34 @@
       <c r="J38" s="13"/>
     </row>
     <row r="39" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="13" t="s">
-        <v>1253</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
+      <c r="A39" s="17" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>877</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
     </row>
     <row r="40" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="17" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D40" s="17" t="s">
         <v>51</v>
@@ -19483,13 +19596,13 @@
     </row>
     <row r="41" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="17" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D41" s="17" t="s">
         <v>51</v>
@@ -19501,15 +19614,15 @@
       <c r="I41" s="17"/>
       <c r="J41" s="17"/>
     </row>
-    <row r="42" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="17" t="s">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>70</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D42" s="17" t="s">
         <v>51</v>
@@ -19518,64 +19631,64 @@
       <c r="F42" s="17"/>
       <c r="G42" s="17"/>
       <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-    </row>
-    <row r="43" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A43" s="17" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="17" t="s">
+      <c r="I42" s="17" t="s">
+        <v>1253</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
         <v>880</v>
       </c>
-      <c r="D43" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17" t="s">
-        <v>1256</v>
-      </c>
-      <c r="J43" s="17" t="s">
+      <c r="B43" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="13" t="s">
         <v>1257</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A44" s="11" t="s">
-        <v>883</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11" t="s">
-        <v>884</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>885</v>
-      </c>
+      <c r="B44" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="13" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>48</v>
@@ -19584,18 +19697,22 @@
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
+      <c r="I45" s="13" t="s">
+        <v>1259</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>1260</v>
+      </c>
     </row>
     <row r="46" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="13" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>48</v>
@@ -19604,22 +19721,18 @@
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
-      <c r="I46" s="13" t="s">
-        <v>1262</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>1263</v>
-      </c>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="13" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>48</v>
@@ -19628,82 +19741,82 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
+      <c r="I47" s="13" t="s">
+        <v>1262</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>1263</v>
+      </c>
     </row>
     <row r="48" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="13" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="17" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+    </row>
+    <row r="49" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="28" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+    </row>
+    <row r="50" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
         <v>883</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13" t="s">
-        <v>1265</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="17" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>883</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-    </row>
-    <row r="50" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="28" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>883</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="28"/>
-      <c r="J50" s="28"/>
-    </row>
-    <row r="51" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>1269</v>
+        <v>867</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="11"/>
@@ -19711,65 +19824,65 @@
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
       <c r="I51" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J51" s="11"/>
-    </row>
-    <row r="52" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A52" s="11" t="s">
-        <v>886</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11" t="s">
-        <v>887</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A53" s="13" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="D53" s="13" t="s">
+        <v>884</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52" s="13" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>883</v>
+      </c>
+      <c r="D52" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13" t="s">
-        <v>1256</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>1257</v>
-      </c>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13" t="s">
+        <v>1253</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="28" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="28"/>
     </row>
     <row r="54" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="28" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B54" s="28" t="s">
         <v>70</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="D54" s="28" t="s">
         <v>51</v>
@@ -19783,13 +19896,13 @@
     </row>
     <row r="55" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="28" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B55" s="28" t="s">
         <v>70</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="D55" s="28" t="s">
         <v>51</v>
@@ -19803,13 +19916,13 @@
     </row>
     <row r="56" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="28" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B56" s="28" t="s">
         <v>70</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="D56" s="28" t="s">
         <v>51</v>
@@ -19821,57 +19934,57 @@
       <c r="I56" s="28"/>
       <c r="J56" s="28"/>
     </row>
-    <row r="57" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="28" t="s">
+    <row r="57" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="11" t="s">
+        <v>886</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="13" t="s">
         <v>1273</v>
       </c>
-      <c r="B57" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" s="28" t="s">
+      <c r="B58" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="D57" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-    </row>
-    <row r="58" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="11" t="s">
-        <v>889</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11" t="s">
-        <v>890</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>891</v>
-      </c>
+      <c r="D58" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
     </row>
     <row r="59" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="13" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>48</v>
@@ -19885,13 +19998,13 @@
     </row>
     <row r="60" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="13" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>48</v>
@@ -19903,57 +20016,61 @@
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
     </row>
-    <row r="61" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="13" t="s">
-        <v>1275</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="13" t="s">
+    <row r="61" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="11" t="s">
         <v>889</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-    </row>
-    <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A62" s="11" t="s">
-        <v>892</v>
-      </c>
-      <c r="B62" s="11" t="s">
+      <c r="B61" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C62" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11" t="s">
-        <v>893</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="C61" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11" t="s">
+        <v>890</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="28" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B62" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>889</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="28"/>
+      <c r="I62" s="28" t="s">
+        <v>1253</v>
+      </c>
+      <c r="J62" s="28" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="28" t="s">
-        <v>1255</v>
+        <v>1283</v>
       </c>
       <c r="B63" s="28" t="s">
         <v>70</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D63" s="28" t="s">
         <v>51</v>
@@ -19962,22 +20079,18 @@
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
       <c r="H63" s="28"/>
-      <c r="I63" s="28" t="s">
-        <v>1256</v>
-      </c>
-      <c r="J63" s="28" t="s">
-        <v>1257</v>
-      </c>
+      <c r="I63" s="28"/>
+      <c r="J63" s="28"/>
     </row>
     <row r="64" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="28" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
       <c r="B64" s="28" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D64" s="28" t="s">
         <v>51</v>
@@ -19986,10 +20099,14 @@
       <c r="F64" s="28"/>
       <c r="G64" s="28"/>
       <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-    </row>
-    <row r="65" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="I64" s="28" t="s">
+        <v>1275</v>
+      </c>
+      <c r="J64" s="28" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="28" t="s">
         <v>1277</v>
       </c>
@@ -19997,10 +20114,10 @@
         <v>70</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E65" s="28"/>
       <c r="F65" s="28"/>
@@ -20021,7 +20138,7 @@
         <v>70</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D66" s="28" t="s">
         <v>54</v>
@@ -20037,49 +20154,53 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="28" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B67" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="28" t="s">
+    <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="11" t="s">
         <v>892</v>
       </c>
-      <c r="D67" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28" t="s">
-        <v>1284</v>
-      </c>
-      <c r="J67" s="28" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A68" s="11" t="s">
+      <c r="B67" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="B68" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>870</v>
-      </c>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="11" t="s">
+      <c r="B68" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G68" s="10"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="10" t="s">
         <v>896</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="J68" s="10" t="s">
         <v>897</v>
       </c>
     </row>
@@ -20091,19 +20212,21 @@
         <v>70</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>74</v>
       </c>
       <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
+      <c r="H69" s="10" t="s">
+        <v>682</v>
+      </c>
       <c r="I69" s="10" t="s">
         <v>899</v>
       </c>
@@ -20119,21 +20242,17 @@
         <v>70</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F70" s="10"/>
       <c r="G70" s="10"/>
-      <c r="H70" s="10" t="s">
-        <v>682</v>
-      </c>
+      <c r="H70" s="10"/>
       <c r="I70" s="10" t="s">
         <v>902</v>
       </c>
@@ -20141,48 +20260,24 @@
         <v>903</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A71" s="10" t="s">
-        <v>904</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>895</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10" t="s">
-        <v>905</v>
-      </c>
-      <c r="J71" s="10" t="s">
-        <v>906</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I23" r:id="rId1" display="voc4cat:0007254" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
-    <hyperlink ref="I24" r:id="rId2" display="voc4cat:0007255" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
-    <hyperlink ref="I28" r:id="rId3" display="voc4cat:0007258" xr:uid="{ECE0B83D-4C10-4937-A571-CB1A78F8D921}"/>
-    <hyperlink ref="I26" r:id="rId4" display="voc4cat:0007256" xr:uid="{B8B87E67-D090-44FF-99F3-C73E22B0384A}"/>
-    <hyperlink ref="I29" r:id="rId5" xr:uid="{AD38AF27-1671-4048-B637-B5B450D15DAD}"/>
-    <hyperlink ref="I35" r:id="rId6" xr:uid="{361B543E-C568-4568-8088-6E70DE9F3B27}"/>
-    <hyperlink ref="I36" r:id="rId7" xr:uid="{1719255A-01AA-4404-94C6-32789CDF8402}"/>
-    <hyperlink ref="I65" r:id="rId8" xr:uid="{67C09C0D-2279-4237-A447-58639A2AE5CC}"/>
+    <hyperlink ref="I22" r:id="rId1" display="voc4cat:0007254" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
+    <hyperlink ref="I23" r:id="rId2" display="voc4cat:0007255" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
+    <hyperlink ref="I27" r:id="rId3" display="voc4cat:0007258" xr:uid="{ECE0B83D-4C10-4937-A571-CB1A78F8D921}"/>
+    <hyperlink ref="I25" r:id="rId4" display="voc4cat:0007256" xr:uid="{B8B87E67-D090-44FF-99F3-C73E22B0384A}"/>
+    <hyperlink ref="I28" r:id="rId5" xr:uid="{AD38AF27-1671-4048-B637-B5B450D15DAD}"/>
+    <hyperlink ref="I34" r:id="rId6" xr:uid="{361B543E-C568-4568-8088-6E70DE9F3B27}"/>
+    <hyperlink ref="I35" r:id="rId7" xr:uid="{1719255A-01AA-4404-94C6-32789CDF8402}"/>
+    <hyperlink ref="I64" r:id="rId8" xr:uid="{67C09C0D-2279-4237-A447-58639A2AE5CC}"/>
     <hyperlink ref="I2" r:id="rId9" xr:uid="{EE99F099-E6BA-477F-A260-88529C3F7434}"/>
     <hyperlink ref="I5" r:id="rId10" xr:uid="{BDA420BA-A173-4F89-A841-856E53112396}"/>
     <hyperlink ref="I9" r:id="rId11" xr:uid="{54581B7D-9C1E-4C15-887D-BA48A1859B95}"/>
     <hyperlink ref="I8" r:id="rId12" xr:uid="{46577A97-6DF9-402F-BCAD-57196F467970}"/>
     <hyperlink ref="I7" r:id="rId13" xr:uid="{11743F2A-1294-4AA1-9B68-D52B44449D93}"/>
     <hyperlink ref="I6" r:id="rId14" xr:uid="{336B9A92-59C1-445E-9AD3-47037654015F}"/>
+    <hyperlink ref="I13" r:id="rId15" xr:uid="{932ABE27-6472-4D48-A472-2C9D929D8E0D}"/>
+    <hyperlink ref="I14" r:id="rId16" xr:uid="{D1FC2FE3-5497-41CC-9559-B84C7DC13A7E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20239,7 +20334,7 @@
     </row>
     <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>70</v>
@@ -20257,15 +20352,15 @@
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>70</v>
@@ -20275,7 +20370,7 @@
         <v>48</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>74</v>
@@ -20285,21 +20380,21 @@
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>48</v>
@@ -20309,21 +20404,21 @@
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>48</v>
@@ -20333,21 +20428,21 @@
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>54</v>
@@ -20360,24 +20455,24 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>54</v>
@@ -20391,21 +20486,21 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>54</v>
@@ -20418,24 +20513,24 @@
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>54</v>
@@ -20449,21 +20544,21 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>54</v>
@@ -20477,21 +20572,21 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>48</v>
@@ -20501,21 +20596,21 @@
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>54</v>
@@ -20529,21 +20624,21 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>54</v>
@@ -20557,21 +20652,21 @@
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>54</v>
@@ -20585,21 +20680,21 @@
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>54</v>
@@ -20613,21 +20708,21 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>48</v>
@@ -20637,21 +20732,21 @@
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>54</v>
@@ -20665,21 +20760,21 @@
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>54</v>
@@ -20692,24 +20787,24 @@
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="10" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>54</v>
@@ -20722,24 +20817,24 @@
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>54</v>
@@ -20753,21 +20848,21 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>54</v>
@@ -20780,24 +20875,24 @@
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>48</v>
@@ -20807,21 +20902,21 @@
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>54</v>
@@ -20834,24 +20929,24 @@
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>54</v>
@@ -20865,21 +20960,21 @@
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>54</v>
@@ -20892,24 +20987,24 @@
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>54</v>
@@ -20922,24 +21017,24 @@
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>54</v>
@@ -20953,21 +21048,21 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>48</v>
@@ -20977,21 +21072,21 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>54</v>
@@ -21005,21 +21100,21 @@
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>54</v>
@@ -21033,21 +21128,21 @@
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>54</v>
@@ -21061,21 +21156,21 @@
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>54</v>
@@ -21089,21 +21184,21 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>54</v>
@@ -21116,24 +21211,24 @@
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>54</v>
@@ -21147,21 +21242,21 @@
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>54</v>
@@ -21175,21 +21270,21 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>48</v>
@@ -21199,21 +21294,21 @@
       <c r="G36" s="11"/>
       <c r="H36" s="11"/>
       <c r="I36" s="11" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>54</v>
@@ -21227,21 +21322,21 @@
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>54</v>
@@ -21255,21 +21350,21 @@
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>54</v>
@@ -21282,30 +21377,30 @@
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>74</v>
@@ -21313,21 +21408,21 @@
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>54</v>
@@ -21341,21 +21436,21 @@
       <c r="G41" s="10"/>
       <c r="H41" s="10"/>
       <c r="I41" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>54</v>
@@ -21369,21 +21464,21 @@
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>48</v>
@@ -21393,21 +21488,21 @@
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>54</v>
@@ -21421,21 +21516,21 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>54</v>
@@ -21448,24 +21543,24 @@
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="10" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>54</v>
@@ -21479,21 +21574,21 @@
       <c r="G46" s="10"/>
       <c r="H46" s="10"/>
       <c r="I46" s="10" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>54</v>
@@ -21507,21 +21602,21 @@
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>54</v>
@@ -21535,21 +21630,21 @@
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
       <c r="I48" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>54</v>
@@ -21563,21 +21658,21 @@
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
       <c r="I49" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>54</v>
@@ -21590,24 +21685,24 @@
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>54</v>
@@ -21621,21 +21716,21 @@
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
       <c r="I51" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>54</v>
@@ -21649,21 +21744,21 @@
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
       <c r="I52" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>48</v>
@@ -21673,21 +21768,21 @@
       <c r="G53" s="11"/>
       <c r="H53" s="11"/>
       <c r="I53" s="11" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>54</v>
@@ -21701,21 +21796,21 @@
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
       <c r="I54" s="10" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>54</v>
@@ -21729,21 +21824,21 @@
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
       <c r="I55" s="10" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>54</v>
@@ -21757,21 +21852,21 @@
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
       <c r="I56" s="10" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>54</v>
@@ -21784,13 +21879,13 @@
       </c>
       <c r="G57" s="10"/>
       <c r="H57" s="10" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
@@ -21801,7 +21896,7 @@
         <v>70</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>54</v>
@@ -21817,13 +21912,13 @@
     </row>
     <row r="59" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>54</v>
@@ -21837,21 +21932,21 @@
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
       <c r="I59" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>54</v>
@@ -21865,21 +21960,21 @@
       <c r="G60" s="10"/>
       <c r="H60" s="10"/>
       <c r="I60" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>48</v>
@@ -21889,21 +21984,21 @@
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
       <c r="I61" s="11" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>54</v>
@@ -21917,21 +22012,21 @@
       <c r="G62" s="10"/>
       <c r="H62" s="10"/>
       <c r="I62" s="10" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>54</v>
@@ -21944,24 +22039,24 @@
       </c>
       <c r="G63" s="10"/>
       <c r="H63" s="10" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>54</v>
@@ -21974,24 +22069,24 @@
       </c>
       <c r="G64" s="10"/>
       <c r="H64" s="10" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>54</v>
@@ -22005,21 +22100,21 @@
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
       <c r="I65" s="10" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>54</v>
@@ -22033,21 +22128,21 @@
       <c r="G66" s="10"/>
       <c r="H66" s="10"/>
       <c r="I66" s="10" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>54</v>
@@ -22061,21 +22156,21 @@
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
       <c r="I67" s="10" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>54</v>
@@ -22089,21 +22184,21 @@
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
       <c r="I68" s="10" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>54</v>
@@ -22117,21 +22212,21 @@
       <c r="G69" s="10"/>
       <c r="H69" s="10"/>
       <c r="I69" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>54</v>
@@ -22145,21 +22240,21 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
       <c r="I70" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>48</v>
@@ -22169,21 +22264,21 @@
       <c r="G71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="11" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>54</v>
@@ -22197,27 +22292,27 @@
       <c r="G72" s="10"/>
       <c r="H72" s="10"/>
       <c r="I72" s="10" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>74</v>
@@ -22225,21 +22320,21 @@
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
       <c r="I73" s="10" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>54</v>
@@ -22253,21 +22348,21 @@
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
       <c r="I74" s="10" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>54</v>
@@ -22280,24 +22375,24 @@
       </c>
       <c r="G75" s="10"/>
       <c r="H75" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>54</v>
@@ -22311,21 +22406,21 @@
       <c r="G76" s="10"/>
       <c r="H76" s="10"/>
       <c r="I76" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>54</v>
@@ -22339,21 +22434,21 @@
       <c r="G77" s="10"/>
       <c r="H77" s="10"/>
       <c r="I77" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>54</v>
@@ -22366,24 +22461,24 @@
       </c>
       <c r="G78" s="10"/>
       <c r="H78" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>54</v>
@@ -22397,21 +22492,21 @@
       <c r="G79" s="10"/>
       <c r="H79" s="10"/>
       <c r="I79" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>54</v>
@@ -22425,21 +22520,21 @@
       <c r="G80" s="10"/>
       <c r="H80" s="10"/>
       <c r="I80" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" s="11" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>48</v>
@@ -22449,21 +22544,21 @@
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
       <c r="I81" s="11" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>54</v>
@@ -22477,21 +22572,21 @@
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="10" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>54</v>
@@ -22504,24 +22599,24 @@
       </c>
       <c r="G83" s="10"/>
       <c r="H83" s="10" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>54</v>
@@ -22535,21 +22630,21 @@
       <c r="G84" s="10"/>
       <c r="H84" s="10"/>
       <c r="I84" s="10" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>54</v>
@@ -22562,24 +22657,24 @@
       </c>
       <c r="G85" s="10"/>
       <c r="H85" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>54</v>
@@ -22592,24 +22687,24 @@
       </c>
       <c r="G86" s="10"/>
       <c r="H86" s="10" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>54</v>
@@ -22623,21 +22718,21 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="10" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>54</v>
@@ -22651,21 +22746,21 @@
       <c r="G88" s="10"/>
       <c r="H88" s="10"/>
       <c r="I88" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>54</v>
@@ -22679,21 +22774,21 @@
       <c r="G89" s="10"/>
       <c r="H89" s="10"/>
       <c r="I89" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" s="11" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>48</v>
@@ -22703,21 +22798,21 @@
       <c r="G90" s="11"/>
       <c r="H90" s="11"/>
       <c r="I90" s="11" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>54</v>
@@ -22731,21 +22826,21 @@
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
       <c r="I91" s="10" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>54</v>
@@ -22759,21 +22854,21 @@
       <c r="G92" s="10"/>
       <c r="H92" s="10"/>
       <c r="I92" s="10" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>54</v>
@@ -22786,24 +22881,24 @@
       </c>
       <c r="G93" s="10"/>
       <c r="H93" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>54</v>
@@ -22817,21 +22912,21 @@
       <c r="G94" s="10"/>
       <c r="H94" s="10"/>
       <c r="I94" s="10" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>54</v>
@@ -22844,30 +22939,30 @@
       </c>
       <c r="G95" s="10"/>
       <c r="H95" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>74</v>
@@ -22875,21 +22970,21 @@
       <c r="G96" s="10"/>
       <c r="H96" s="10"/>
       <c r="I96" s="10" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>54</v>
@@ -22902,24 +22997,24 @@
       </c>
       <c r="G97" s="10"/>
       <c r="H97" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>54</v>
@@ -22933,21 +23028,21 @@
       <c r="G98" s="10"/>
       <c r="H98" s="10"/>
       <c r="I98" s="10" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>54</v>
@@ -22961,21 +23056,21 @@
       <c r="G99" s="10"/>
       <c r="H99" s="10"/>
       <c r="I99" s="10" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>54</v>
@@ -22988,24 +23083,24 @@
       </c>
       <c r="G100" s="10"/>
       <c r="H100" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>54</v>
@@ -23019,21 +23114,21 @@
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
       <c r="I101" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>54</v>
@@ -23047,10 +23142,10 @@
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
       <c r="I102" s="10" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
@@ -23065,19 +23160,19 @@
         <v>48</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="9"/>
       <c r="J103" s="9" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A104" s="11" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>103</v>
@@ -23096,18 +23191,18 @@
         <v>123</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" s="11" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>48</v>
@@ -23117,21 +23212,21 @@
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
       <c r="I105" s="11" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>54</v>
@@ -23145,21 +23240,21 @@
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
       <c r="I106" s="10" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>54</v>
@@ -23172,24 +23267,24 @@
       </c>
       <c r="G107" s="10"/>
       <c r="H107" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>54</v>
@@ -23203,21 +23298,21 @@
       <c r="G108" s="10"/>
       <c r="H108" s="10"/>
       <c r="I108" s="10" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>54</v>
@@ -23231,27 +23326,27 @@
       <c r="G109" s="10"/>
       <c r="H109" s="10"/>
       <c r="I109" s="10" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="F110" s="10" t="s">
         <v>74</v>
@@ -23259,21 +23354,21 @@
       <c r="G110" s="10"/>
       <c r="H110" s="10"/>
       <c r="I110" s="10" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>54</v>
@@ -23286,24 +23381,24 @@
       </c>
       <c r="G111" s="10"/>
       <c r="H111" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>48</v>
@@ -23313,21 +23408,21 @@
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
       <c r="I112" s="11" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>54</v>
@@ -23341,21 +23436,21 @@
       <c r="G113" s="10"/>
       <c r="H113" s="10"/>
       <c r="I113" s="10" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>54</v>
@@ -23368,24 +23463,24 @@
       </c>
       <c r="G114" s="10"/>
       <c r="H114" s="10" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>54</v>
@@ -23398,24 +23493,24 @@
       </c>
       <c r="G115" s="10"/>
       <c r="H115" s="10" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>54</v>
@@ -23429,21 +23524,21 @@
       <c r="G116" s="10"/>
       <c r="H116" s="10"/>
       <c r="I116" s="10" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>54</v>
@@ -23457,21 +23552,21 @@
       <c r="G117" s="10"/>
       <c r="H117" s="10"/>
       <c r="I117" s="10" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A118" s="11" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>48</v>
@@ -23481,21 +23576,21 @@
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
       <c r="I118" s="11" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>54</v>
@@ -23509,21 +23604,21 @@
       <c r="G119" s="10"/>
       <c r="H119" s="10"/>
       <c r="I119" s="10" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>54</v>
@@ -23537,10 +23632,10 @@
       <c r="G120" s="10"/>
       <c r="H120" s="10"/>
       <c r="I120" s="10" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.35">
@@ -23551,7 +23646,7 @@
         <v>70</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>54</v>
@@ -23567,13 +23662,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>54</v>
@@ -23589,13 +23684,13 @@
     </row>
     <row r="123" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>54</v>
@@ -23609,21 +23704,21 @@
       <c r="G123" s="10"/>
       <c r="H123" s="10"/>
       <c r="I123" s="10" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>54</v>
@@ -23636,24 +23731,24 @@
       </c>
       <c r="G124" s="10"/>
       <c r="H124" s="10" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A125" s="11" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D125" s="11" t="s">
         <v>48</v>
@@ -23663,21 +23758,21 @@
       <c r="G125" s="11"/>
       <c r="H125" s="11"/>
       <c r="I125" s="11" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>54</v>
@@ -23691,21 +23786,21 @@
       <c r="G126" s="10"/>
       <c r="H126" s="10"/>
       <c r="I126" s="10" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>54</v>
@@ -23719,10 +23814,10 @@
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
       <c r="I127" s="10" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.35">
@@ -23733,7 +23828,7 @@
         <v>70</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>54</v>
@@ -23749,13 +23844,13 @@
     </row>
     <row r="129" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="B129" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>54</v>
@@ -23769,21 +23864,21 @@
       <c r="G129" s="10"/>
       <c r="H129" s="10"/>
       <c r="I129" s="10" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="B130" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>54</v>
@@ -23797,21 +23892,21 @@
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
       <c r="I130" s="10" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B131" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>54</v>
@@ -23825,21 +23920,21 @@
       <c r="G131" s="10"/>
       <c r="H131" s="10"/>
       <c r="I131" s="10" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="B132" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D132" s="10" t="s">
         <v>54</v>
@@ -23853,10 +23948,10 @@
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
       <c r="I132" s="10" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
   </sheetData>

--- a/inbox/coremeta4cat_vocabulary.xlsx
+++ b/inbox/coremeta4cat_vocabulary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Mohammad\03_Projects\NFDI4Cat-2.0\task_forces\coremeta4cat\data_analysis\005\pushed_to_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9259E7EA-5FC8-4E91-ABD3-4D232EE003BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C444BC-D3CC-4B3D-87AE-61D3BDB82882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31830" yWindow="3090" windowWidth="25170" windowHeight="15000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5195" uniqueCount="1315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5321" uniqueCount="1388">
   <si>
     <t>CoreMeta4Cat Vocabulary Reference Workbook</t>
   </si>
@@ -2670,20 +2670,7 @@
 component as a separate ChemicalEntity and record composition via has_concentration.</t>
   </si>
   <si>
-    <t>catalyst type</t>
-  </si>
-  <si>
-    <t>VOC4CAT:0007014</t>
-  </si>
-  <si>
-    <t>Type of catalyst used (e.g. heterogeneous, homogeneous, biocatalyst).
-For heterogeneous catalysts, use voc4cat terms where available.</t>
-  </si>
-  <si>
     <t>product identification method</t>
-  </si>
-  <si>
-    <t>ProductIdentificationMethod</t>
   </si>
   <si>
     <t>coremeta4cat:product_identification_method</t>
@@ -2692,14 +2679,6 @@
     <t>The analytical method used to identify and/or quantify reaction products.
 Should reference a CharacterizationTechnique instance (e.g. GCMS, HPLC_MS).
 The abstract stub ProductIdentificationMethod is retained for backward compatibility.</t>
-  </si>
-  <si>
-    <t>Abstract Plan representing the method used to identify and quantify reaction
-products. In practice, users should reference a concrete CharacterizationTechnique
-subclass from coremeta4cat_characterization_ap (e.g. GCMS, HPLC_MS, NMRSpectroscopy).
-This abstract class is retained for backward compatibility with the original
-CoreMeta4Cat monolith. It is a subclass of Plan (prov:Plan / OBI:0000272) so that
-it can participate in the realized_plan slot if needed.</t>
   </si>
   <si>
     <t>carried out by</t>
@@ -4147,6 +4126,240 @@
   </si>
   <si>
     <t>A substance that increases the rate of a chemical reaction that is in the phase as the reagents.</t>
+  </si>
+  <si>
+    <t>has product identification method</t>
+  </si>
+  <si>
+    <t>Chemical Reaction</t>
+  </si>
+  <si>
+    <t>voc4cat:0007010</t>
+  </si>
+  <si>
+    <t>A group of chemical reactions with common conditions or reactants, e.g. Oxidation, Hydrogenation, Reduction, Cracking.</t>
+  </si>
+  <si>
+    <t>hydrogenation</t>
+  </si>
+  <si>
+    <t>reaction type</t>
+  </si>
+  <si>
+    <t>voc4cat:0000260</t>
+  </si>
+  <si>
+    <t>A chemical reaction of molecular hydrogen (H2) and another chemical species, typically facilitated by a catalyst.</t>
+  </si>
+  <si>
+    <t>oxidation</t>
+  </si>
+  <si>
+    <t>voc4cat:0000097</t>
+  </si>
+  <si>
+    <t>The loss of electrons or an increase in the oxidation state of a species.</t>
+  </si>
+  <si>
+    <t>dehydrogenation</t>
+  </si>
+  <si>
+    <t>voc4cat:0000297</t>
+  </si>
+  <si>
+    <t>A chemical reaction that involves the removal of two or more hydrogen atoms from a molecule.</t>
+  </si>
+  <si>
+    <t>has Reaction Type</t>
+  </si>
+  <si>
+    <t>voc4cat:0000183</t>
+  </si>
+  <si>
+    <t>An occurrence or happening, marked by a specific point in time. Events can be observed, recorded, and may have an impact on the state of the system or entities involved.</t>
+  </si>
+  <si>
+    <t>has events</t>
+  </si>
+  <si>
+    <t>C-C coupling reaction</t>
+  </si>
+  <si>
+    <t>voc4cat:0000223</t>
+  </si>
+  <si>
+    <t>A chemical reaction where a carbon-carbon bond is formed from two carbon-containing fragments.</t>
+  </si>
+  <si>
+    <t>hydrodeoxygenation</t>
+  </si>
+  <si>
+    <t>voc4cat:0000226</t>
+  </si>
+  <si>
+    <t>A catalytic process in which oxygen is removed from oxygenated organic compounds using hydrogen.</t>
+  </si>
+  <si>
+    <t>oxygen evolution reaction</t>
+  </si>
+  <si>
+    <t>voc4cat:0000236</t>
+  </si>
+  <si>
+    <t>A chemical reaction of generating molecular oxygen in electrochemistry.</t>
+  </si>
+  <si>
+    <t>carbonylation</t>
+  </si>
+  <si>
+    <t>voc4cat:0000247</t>
+  </si>
+  <si>
+    <t>A chemical reaction in which a carbonyl group (C=O) is introduced into a molecule, typically through the addition of carbon monoxide (CO) to a substrate.</t>
+  </si>
+  <si>
+    <t>hydroxylation</t>
+  </si>
+  <si>
+    <t>voc4cat:0000258</t>
+  </si>
+  <si>
+    <t>The addition of a hydroxyl group (-OH) to a molecule, typically by replacing a hydrogen atom.</t>
+  </si>
+  <si>
+    <t>CO2 hydrogenation</t>
+  </si>
+  <si>
+    <t>voc4cat:0000259</t>
+  </si>
+  <si>
+    <t>The reaction of carbon dioxide (CO2) with molecular hydrogen (H2) to produce value-added hydrocarbons or alcohols.</t>
+  </si>
+  <si>
+    <t>selective oxidation</t>
+  </si>
+  <si>
+    <t>voc4cat:0000261</t>
+  </si>
+  <si>
+    <t>The targeted oxidation of a specific bond or functional group in a molecule leaving other sites unaffected, often directed by a catalyst.</t>
+  </si>
+  <si>
+    <t>Fischer-Tropsch synthesis</t>
+  </si>
+  <si>
+    <t>voc4cat:0000280</t>
+  </si>
+  <si>
+    <t>A catalytic chemical reaction in which a mixture of carbon monoxide (CO) and hydrogen (H2), is converted via a chain-growth mechanism into long-chain hydrocarbons (e.g., alkanes, alkenes or alcohols)—typically using iron or cobalt catalysts under moderate to high pressures and temperatures.</t>
+  </si>
+  <si>
+    <t>CO oxidation</t>
+  </si>
+  <si>
+    <t>voc4cat:0000289</t>
+  </si>
+  <si>
+    <t>The reaction in which carbon monoxide (CO) is converted to carbon dioxide (CO₂) through interaction with an oxidizing agent, typically oxygen (O₂).</t>
+  </si>
+  <si>
+    <t>CatalystType</t>
+  </si>
+  <si>
+    <t>hasCatalystType</t>
+  </si>
+  <si>
+    <t>thin film</t>
+  </si>
+  <si>
+    <t>voc4cat:0000019</t>
+  </si>
+  <si>
+    <t>A catalyst introduced to the reaction chamber in the form of a thin film. To form a thin film, a (powdered) catalyst is deposited on a substrate (e.g., glass or metal) using an appropriate deposition technique.</t>
+  </si>
+  <si>
+    <t>bulk catalyst</t>
+  </si>
+  <si>
+    <t>voc4cat:0007015</t>
+  </si>
+  <si>
+    <t>A catalyst that consists mainly of the active ingredient or phase.</t>
+  </si>
+  <si>
+    <t>powdered catalyst</t>
+  </si>
+  <si>
+    <t>voc4cat:0000017</t>
+  </si>
+  <si>
+    <t>A catalyst introduced to the reaction chamber in the form of a powder.</t>
+  </si>
+  <si>
+    <t>deposited sample</t>
+  </si>
+  <si>
+    <t>voc4cat:0000038</t>
+  </si>
+  <si>
+    <t>A thin film of the catalyst deposited on an appropriate for the application substrate.</t>
+  </si>
+  <si>
+    <t>photocatalyst</t>
+  </si>
+  <si>
+    <t>voc4cat:0000002</t>
+  </si>
+  <si>
+    <t>A material that absorbs photons (light) of appropriate energy and initiates or accelerates a photochemical reaction, while it regenerates itself after each reaction cycle.</t>
+  </si>
+  <si>
+    <t>supported catalyst</t>
+  </si>
+  <si>
+    <t>voc4cat:0007034</t>
+  </si>
+  <si>
+    <t>A catalyst where the active material is usually the minority phase and fixed on a high surface area, relatively inert solid.</t>
+  </si>
+  <si>
+    <t>liquid phase analysis</t>
+  </si>
+  <si>
+    <t>voc4cat:0007813</t>
+  </si>
+  <si>
+    <t>Analysis of the liquid sample from a catalytic test.</t>
+  </si>
+  <si>
+    <t>gas phase analysis</t>
+  </si>
+  <si>
+    <t>voc4cat:0007814</t>
+  </si>
+  <si>
+    <t>Analysis of the gaseous sample from a catalytic test.</t>
+  </si>
+  <si>
+    <t>Chromatographic Methods</t>
+  </si>
+  <si>
+    <t>Gas Chromatography (GC)</t>
+  </si>
+  <si>
+    <t>Gas Chromatography–Mass Spectrometry (GC-MS)</t>
+  </si>
+  <si>
+    <t>High Performance Liquid Chromatography (HPLC)</t>
+  </si>
+  <si>
+    <t>Spectroscopic Methods</t>
+  </si>
+  <si>
+    <t>Mass Spectrometry (MS)</t>
+  </si>
+  <si>
+    <t>Fourier Transform Infrared Spectroscopy (FTIR)</t>
   </si>
 </sst>
 </file>
@@ -4196,7 +4409,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4286,12 +4499,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -4421,26 +4646,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
       <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4448,7 +4664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -4545,16 +4761,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4567,22 +4774,47 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4895,17 +5127,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
+      <c r="B1" s="40"/>
     </row>
     <row r="2" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="35"/>
+      <c r="B3" s="40"/>
     </row>
     <row r="4" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -4941,10 +5173,10 @@
     </row>
     <row r="8" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="40"/>
     </row>
     <row r="10" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -5004,10 +5236,10 @@
     </row>
     <row r="17" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="35"/>
+      <c r="B18" s="40"/>
     </row>
     <row r="19" spans="1:2" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -5111,19 +5343,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="2" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -5160,11 +5392,11 @@
     </row>
     <row r="7" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
     </row>
     <row r="9" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -5248,18 +5480,18 @@
     </row>
     <row r="19" spans="1:3" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
     </row>
     <row r="21" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -18659,10 +18891,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118C8BAC-9B70-4E7A-BFF0-9A2BB55A4E4D}">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
@@ -18707,8 +18939,8 @@
       </c>
     </row>
     <row r="2" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="38" t="s">
-        <v>1285</v>
+      <c r="A2" s="35" t="s">
+        <v>1280</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>70</v>
@@ -18722,15 +18954,15 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="38" t="s">
-        <v>1284</v>
+      <c r="A3" s="35" t="s">
+        <v>1279</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>70</v>
@@ -18747,8 +18979,8 @@
       <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="38" t="s">
-        <v>1303</v>
+      <c r="A4" s="35" t="s">
+        <v>1298</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>70</v>
@@ -18758,7 +18990,7 @@
         <v>51</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>74</v>
@@ -18771,14 +19003,14 @@
       <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="38" t="s">
-        <v>1288</v>
+      <c r="A5" s="35" t="s">
+        <v>1283</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>51</v>
@@ -18788,21 +19020,21 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="39" t="s">
-        <v>1291</v>
+      <c r="A6" s="36" t="s">
+        <v>1286</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
@@ -18810,21 +19042,21 @@
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
       <c r="I6" s="23" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="12" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="39" t="s">
-        <v>1294</v>
+      <c r="A7" s="36" t="s">
+        <v>1289</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
@@ -18832,21 +19064,21 @@
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
       <c r="I7" s="30" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="12" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="39" t="s">
-        <v>1297</v>
+      <c r="A8" s="36" t="s">
+        <v>1292</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
@@ -18854,21 +19086,21 @@
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
       <c r="I8" s="23" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="12" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A9" s="40" t="s">
-        <v>1300</v>
+      <c r="A9" s="37" t="s">
+        <v>1295</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
@@ -18876,10 +19108,10 @@
       <c r="G9" s="32"/>
       <c r="H9" s="32"/>
       <c r="I9" s="30" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
@@ -18910,7 +19142,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>855</v>
       </c>
@@ -18938,865 +19170,821 @@
         <v>857</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
+    <row r="12" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="43" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="9" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9" t="s">
+        <v>1312</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="38" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J14" s="38" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="38" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38" t="s">
+        <v>1319</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="38" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38" t="s">
+        <v>1322</v>
+      </c>
+      <c r="J16" s="38" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="34" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="45" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="44"/>
+      <c r="D17" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="46" t="s">
+        <v>1325</v>
+      </c>
+      <c r="J17" s="27" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="38" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38" t="s">
+        <v>1329</v>
+      </c>
+      <c r="J18" s="38" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="38" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38" t="s">
+        <v>1332</v>
+      </c>
+      <c r="J19" s="38" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="38" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38" t="s">
+        <v>1335</v>
+      </c>
+      <c r="J20" s="38" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="34" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="38" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38" t="s">
+        <v>1338</v>
+      </c>
+      <c r="J21" s="38" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="38" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38" t="s">
+        <v>1341</v>
+      </c>
+      <c r="J22" s="38" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="38" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38" t="s">
+        <v>1344</v>
+      </c>
+      <c r="J23" s="38" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="34" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="38" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38" t="s">
+        <v>1347</v>
+      </c>
+      <c r="J24" s="38" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="38" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38" t="s">
+        <v>1350</v>
+      </c>
+      <c r="J25" s="38" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="34" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="38" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38" t="s">
+        <v>1353</v>
+      </c>
+      <c r="J26" s="38" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="18" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="38" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J28" s="38" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="38" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38" t="s">
+        <v>1304</v>
+      </c>
+      <c r="J29" s="38" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="38" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J30" s="38"/>
+    </row>
+    <row r="31" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="38" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38" t="s">
+        <v>1308</v>
+      </c>
+      <c r="J31" s="38" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="47" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B32" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="49" t="s">
+        <v>1358</v>
+      </c>
+      <c r="J32" s="50" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="51" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="52" t="s">
+        <v>1361</v>
+      </c>
+      <c r="J33" s="53" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="47" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="49" t="s">
+        <v>1364</v>
+      </c>
+      <c r="J34" s="50" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="51" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="52" t="s">
+        <v>1367</v>
+      </c>
+      <c r="J35" s="53" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="47" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B36" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="49" t="s">
+        <v>1370</v>
+      </c>
+      <c r="J36" s="50" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="51" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B37" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="52" t="s">
+        <v>1373</v>
+      </c>
+      <c r="J37" s="53" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="18" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18" t="s">
+        <v>859</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="51" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="51" t="s">
         <v>858</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8" t="s">
-        <v>859</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="46" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B13" s="41" t="s">
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51" t="s">
+        <v>1376</v>
+      </c>
+      <c r="J39" s="51" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="51" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B40" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C40" s="51" t="s">
         <v>858</v>
       </c>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="42" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J13" s="43" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="46" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B14" s="41" t="s">
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51" t="s">
+        <v>1379</v>
+      </c>
+      <c r="J40" s="51" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="51" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B41" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C41" s="51" t="s">
         <v>858</v>
       </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41" t="s">
-        <v>1309</v>
-      </c>
-      <c r="J14" s="41" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="47" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B15" s="41" t="s">
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+    </row>
+    <row r="42" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="51" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B42" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C42" s="51" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+    </row>
+    <row r="43" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="51" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B43" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
+    </row>
+    <row r="44" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="51" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B44" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="51" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+    </row>
+    <row r="45" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="51" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B45" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="51" t="s">
         <v>858</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="44" t="s">
-        <v>1311</v>
-      </c>
-      <c r="J15" s="45"/>
-    </row>
-    <row r="16" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="47" t="s">
-        <v>1312</v>
-      </c>
-      <c r="B16" s="41" t="s">
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+    </row>
+    <row r="46" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="51" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B46" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="41" t="s">
-        <v>858</v>
-      </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="44" t="s">
-        <v>1313</v>
-      </c>
-      <c r="J16" s="43" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="87" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
+      <c r="C46" s="51" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="51"/>
+    </row>
+    <row r="47" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="51" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B47" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D47" s="51"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="51"/>
+    </row>
+    <row r="48" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="9" t="s">
         <v>861</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9" t="s">
+      <c r="B48" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E48" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9" t="s">
+      <c r="F48" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9" t="s">
         <v>863</v>
       </c>
-      <c r="J17" s="9" t="s">
+    </row>
+    <row r="49" spans="1:10" s="12" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+      <c r="A49" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="174" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>862</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>861</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="J18" s="11" t="s">
+      <c r="J49" s="9" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
+    <row r="50" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" s="11" t="s">
         <v>866</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="145" x14ac:dyDescent="0.35">
-      <c r="A20" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>866</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9" t="s">
-        <v>869</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>871</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11" t="s">
-        <v>872</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="13" t="s">
-        <v>1225</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>871</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="16" t="s">
-        <v>1218</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="13" t="s">
-        <v>1226</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>871</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="16" t="s">
-        <v>1219</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>871</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18" t="s">
-        <v>1221</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
-        <v>1229</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11" t="s">
-        <v>1232</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="20" t="s">
-        <v>1227</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>871</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21" t="s">
-        <v>1228</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="20" t="s">
-        <v>1233</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>871</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20" t="s">
-        <v>1234</v>
-      </c>
-      <c r="J28" s="20" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
-        <v>874</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11" t="s">
-        <v>875</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>874</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13" t="s">
-        <v>1241</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
-        <v>1243</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>874</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-    </row>
-    <row r="32" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="17" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>874</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="20" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>874</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="27"/>
-    </row>
-    <row r="34" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A34" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="B34" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>874</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J34" s="21" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="21" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>874</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="21" t="s">
-        <v>1246</v>
-      </c>
-      <c r="J35" s="21" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="11" t="s">
-        <v>877</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11" t="s">
-        <v>878</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="13" t="s">
-        <v>1249</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>877</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
-        <v>1250</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>877</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-    </row>
-    <row r="39" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="17" t="s">
-        <v>1251</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>877</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-    </row>
-    <row r="40" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="17" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="17" t="s">
-        <v>877</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-    </row>
-    <row r="41" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="17" t="s">
-        <v>1256</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>877</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-    </row>
-    <row r="42" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="17" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>877</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17" t="s">
-        <v>1253</v>
-      </c>
-      <c r="J42" s="17" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A43" s="11" t="s">
-        <v>880</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11" t="s">
-        <v>881</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="13" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-    </row>
-    <row r="45" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="13" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13" t="s">
-        <v>1259</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="13" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-    </row>
-    <row r="47" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="13" t="s">
-        <v>1261</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13" t="s">
-        <v>1262</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="17" t="s">
-        <v>1265</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>880</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-    </row>
-    <row r="49" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="28" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B49" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>880</v>
-      </c>
-      <c r="D49" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-    </row>
-    <row r="50" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>1266</v>
+        <v>862</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
@@ -19804,187 +19992,203 @@
       <c r="G50" s="11"/>
       <c r="H50" s="11"/>
       <c r="I50" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="J50" s="11"/>
-    </row>
-    <row r="51" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
-        <v>883</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="11" t="s">
         <v>867</v>
       </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11" t="s">
-        <v>884</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>885</v>
+      <c r="J50" s="11" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="13" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>866</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="16" t="s">
+        <v>1213</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>1211</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="13" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>883</v>
-      </c>
-      <c r="D52" s="13" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>866</v>
+      </c>
+      <c r="D52" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13" t="s">
-        <v>1253</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="28" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>883</v>
-      </c>
-      <c r="D53" s="28" t="s">
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="16" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="12" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>866</v>
+      </c>
+      <c r="D53" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-    </row>
-    <row r="54" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="28" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B54" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" s="28" t="s">
-        <v>883</v>
-      </c>
-      <c r="D54" s="28" t="s">
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J53" s="19" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A54" s="11" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="11" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+    </row>
+    <row r="56" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="20" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>866</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21" t="s">
+        <v>1223</v>
+      </c>
+      <c r="J56" s="22" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="20" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>866</v>
+      </c>
+      <c r="D57" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28"/>
-    </row>
-    <row r="55" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="28" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="28" t="s">
-        <v>883</v>
-      </c>
-      <c r="D55" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-    </row>
-    <row r="56" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="28" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B56" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="28" t="s">
-        <v>883</v>
-      </c>
-      <c r="D56" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
-      <c r="J56" s="28"/>
-    </row>
-    <row r="57" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="11" t="s">
-        <v>886</v>
-      </c>
-      <c r="B57" s="11" t="s">
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20" t="s">
+        <v>1229</v>
+      </c>
+      <c r="J57" s="20" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="11" t="s">
+        <v>869</v>
+      </c>
+      <c r="B58" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11" t="s">
-        <v>887</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="13" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>886</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C58" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="13" t="s">
-        <v>1271</v>
+        <v>1235</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>886</v>
+        <v>869</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>48</v>
@@ -19993,18 +20197,22 @@
       <c r="F59" s="13"/>
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
+      <c r="I59" s="13" t="s">
+        <v>1236</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>1237</v>
+      </c>
     </row>
     <row r="60" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="13" t="s">
-        <v>1272</v>
+        <v>1238</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>886</v>
+        <v>869</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>48</v>
@@ -20016,270 +20224,908 @@
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
     </row>
-    <row r="61" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A61" s="11" t="s">
+    <row r="61" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="17" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17" t="s">
+        <v>1233</v>
+      </c>
+      <c r="J61" s="17" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="20" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>869</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="27"/>
+    </row>
+    <row r="63" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>869</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="21" t="s">
+        <v>1240</v>
+      </c>
+      <c r="J63" s="21" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="21" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>869</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="21" t="s">
+        <v>1241</v>
+      </c>
+      <c r="J64" s="21" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11" t="s">
+        <v>873</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="13" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>872</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+    </row>
+    <row r="67" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="13" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>872</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="17" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+    </row>
+    <row r="69" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="17" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="17"/>
+    </row>
+    <row r="70" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="17" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="17"/>
+    </row>
+    <row r="71" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="17" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17" t="s">
+        <v>1248</v>
+      </c>
+      <c r="J71" s="17" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A72" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="13" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>875</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+    </row>
+    <row r="74" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="13" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>875</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13" t="s">
+        <v>1254</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="13" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>875</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+    </row>
+    <row r="76" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="13" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>875</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13" t="s">
+        <v>1257</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="17" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B77" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>875</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+    </row>
+    <row r="78" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="28" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B78" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>875</v>
+      </c>
+      <c r="D78" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="28"/>
+      <c r="J78" s="28"/>
+    </row>
+    <row r="79" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="J79" s="11"/>
+    </row>
+    <row r="80" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A80" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11" t="s">
+        <v>879</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A81" s="13" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>878</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13" t="s">
+        <v>1248</v>
+      </c>
+      <c r="J81" s="13" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="28" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B82" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C82" s="28" t="s">
+        <v>878</v>
+      </c>
+      <c r="D82" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E82" s="28"/>
+      <c r="F82" s="28"/>
+      <c r="G82" s="28"/>
+      <c r="H82" s="28"/>
+      <c r="I82" s="28"/>
+      <c r="J82" s="28"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="28" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>878</v>
+      </c>
+      <c r="D83" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" s="28"/>
+      <c r="F83" s="28"/>
+      <c r="G83" s="28"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="28"/>
+      <c r="J83" s="28"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="28" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C84" s="28" t="s">
+        <v>878</v>
+      </c>
+      <c r="D84" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="28"/>
+      <c r="J84" s="28"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="28" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B85" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C85" s="28" t="s">
+        <v>878</v>
+      </c>
+      <c r="D85" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E85" s="28"/>
+      <c r="F85" s="28"/>
+      <c r="G85" s="28"/>
+      <c r="H85" s="28"/>
+      <c r="I85" s="28"/>
+      <c r="J85" s="28"/>
+    </row>
+    <row r="86" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A86" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="13" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>881</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
+      <c r="J87" s="13"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="13" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>881</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="13"/>
+      <c r="J88" s="13"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="13" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>881</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="13"/>
+    </row>
+    <row r="90" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A90" s="11" t="s">
+        <v>884</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11" t="s">
+        <v>885</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A91" s="28" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B91" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C91" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="D91" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28"/>
+      <c r="H91" s="28"/>
+      <c r="I91" s="28" t="s">
+        <v>1248</v>
+      </c>
+      <c r="J91" s="28" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="28" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B92" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C92" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="D92" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="28"/>
+      <c r="J92" s="28"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" s="28" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B93" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="D93" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="28" t="s">
+        <v>1270</v>
+      </c>
+      <c r="J93" s="28" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A94" s="28" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B94" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C94" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="D94" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="28" t="s">
+        <v>1273</v>
+      </c>
+      <c r="J94" s="28" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A95" s="28" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B95" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C95" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="D95" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E95" s="28"/>
+      <c r="F95" s="28"/>
+      <c r="G95" s="28"/>
+      <c r="H95" s="28"/>
+      <c r="I95" s="28" t="s">
+        <v>1276</v>
+      </c>
+      <c r="J95" s="28" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A96" s="11" t="s">
+        <v>887</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11" t="s">
+        <v>888</v>
+      </c>
+      <c r="J96" s="11" t="s">
         <v>889</v>
       </c>
-      <c r="B61" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11" t="s">
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="10" t="s">
         <v>890</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="B97" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G97" s="10"/>
+      <c r="H97" s="10"/>
+      <c r="I97" s="10" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A62" s="28" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B62" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="28" t="s">
-        <v>889</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="28" t="s">
-        <v>1253</v>
-      </c>
-      <c r="J62" s="28" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="28" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B63" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="28" t="s">
-        <v>889</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="28"/>
-    </row>
-    <row r="64" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="28" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B64" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="28" t="s">
-        <v>889</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28" t="s">
-        <v>1275</v>
-      </c>
-      <c r="J64" s="28" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A65" s="28" t="s">
-        <v>1277</v>
-      </c>
-      <c r="B65" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="28" t="s">
-        <v>889</v>
-      </c>
-      <c r="D65" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E65" s="28"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
-      <c r="H65" s="28"/>
-      <c r="I65" s="28" t="s">
-        <v>1278</v>
-      </c>
-      <c r="J65" s="28" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A66" s="28" t="s">
-        <v>1280</v>
-      </c>
-      <c r="B66" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" s="28" t="s">
-        <v>889</v>
-      </c>
-      <c r="D66" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="E66" s="28"/>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="28" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J66" s="28" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="11" t="s">
+      <c r="J97" s="10" t="s">
         <v>892</v>
       </c>
-      <c r="B67" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>867</v>
-      </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11" t="s">
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A98" s="10" t="s">
         <v>893</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="B98" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G98" s="10"/>
+      <c r="H98" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="I98" s="10" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A68" s="10" t="s">
+      <c r="J98" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>892</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E68" s="10" t="s">
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E99" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F68" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10" t="s">
-        <v>896</v>
-      </c>
-      <c r="J68" s="10" t="s">
+      <c r="F99" s="10"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A69" s="10" t="s">
+      <c r="J99" s="10" t="s">
         <v>898</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>892</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10" t="s">
-        <v>682</v>
-      </c>
-      <c r="I69" s="10" t="s">
-        <v>899</v>
-      </c>
-      <c r="J69" s="10" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A70" s="10" t="s">
-        <v>901</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>892</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10" t="s">
-        <v>902</v>
-      </c>
-      <c r="J70" s="10" t="s">
-        <v>903</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I22" r:id="rId1" display="voc4cat:0007254" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
-    <hyperlink ref="I23" r:id="rId2" display="voc4cat:0007255" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
-    <hyperlink ref="I27" r:id="rId3" display="voc4cat:0007258" xr:uid="{ECE0B83D-4C10-4937-A571-CB1A78F8D921}"/>
-    <hyperlink ref="I25" r:id="rId4" display="voc4cat:0007256" xr:uid="{B8B87E67-D090-44FF-99F3-C73E22B0384A}"/>
-    <hyperlink ref="I28" r:id="rId5" xr:uid="{AD38AF27-1671-4048-B637-B5B450D15DAD}"/>
-    <hyperlink ref="I34" r:id="rId6" xr:uid="{361B543E-C568-4568-8088-6E70DE9F3B27}"/>
-    <hyperlink ref="I35" r:id="rId7" xr:uid="{1719255A-01AA-4404-94C6-32789CDF8402}"/>
-    <hyperlink ref="I64" r:id="rId8" xr:uid="{67C09C0D-2279-4237-A447-58639A2AE5CC}"/>
+    <hyperlink ref="I51" r:id="rId1" display="voc4cat:0007254" xr:uid="{29259935-27A1-420E-91B6-F764B122D2E9}"/>
+    <hyperlink ref="I52" r:id="rId2" display="voc4cat:0007255" xr:uid="{A3CE405B-A277-421B-8F7E-EA2CD3486A6C}"/>
+    <hyperlink ref="I56" r:id="rId3" display="voc4cat:0007258" xr:uid="{ECE0B83D-4C10-4937-A571-CB1A78F8D921}"/>
+    <hyperlink ref="I54" r:id="rId4" display="voc4cat:0007256" xr:uid="{B8B87E67-D090-44FF-99F3-C73E22B0384A}"/>
+    <hyperlink ref="I57" r:id="rId5" xr:uid="{AD38AF27-1671-4048-B637-B5B450D15DAD}"/>
+    <hyperlink ref="I63" r:id="rId6" xr:uid="{361B543E-C568-4568-8088-6E70DE9F3B27}"/>
+    <hyperlink ref="I64" r:id="rId7" xr:uid="{1719255A-01AA-4404-94C6-32789CDF8402}"/>
+    <hyperlink ref="I93" r:id="rId8" xr:uid="{67C09C0D-2279-4237-A447-58639A2AE5CC}"/>
     <hyperlink ref="I2" r:id="rId9" xr:uid="{EE99F099-E6BA-477F-A260-88529C3F7434}"/>
     <hyperlink ref="I5" r:id="rId10" xr:uid="{BDA420BA-A173-4F89-A841-856E53112396}"/>
     <hyperlink ref="I9" r:id="rId11" xr:uid="{54581B7D-9C1E-4C15-887D-BA48A1859B95}"/>
     <hyperlink ref="I8" r:id="rId12" xr:uid="{46577A97-6DF9-402F-BCAD-57196F467970}"/>
     <hyperlink ref="I7" r:id="rId13" xr:uid="{11743F2A-1294-4AA1-9B68-D52B44449D93}"/>
     <hyperlink ref="I6" r:id="rId14" xr:uid="{336B9A92-59C1-445E-9AD3-47037654015F}"/>
-    <hyperlink ref="I13" r:id="rId15" xr:uid="{932ABE27-6472-4D48-A472-2C9D929D8E0D}"/>
-    <hyperlink ref="I14" r:id="rId16" xr:uid="{D1FC2FE3-5497-41CC-9559-B84C7DC13A7E}"/>
+    <hyperlink ref="I28" r:id="rId15" xr:uid="{932ABE27-6472-4D48-A472-2C9D929D8E0D}"/>
+    <hyperlink ref="I29" r:id="rId16" xr:uid="{D1FC2FE3-5497-41CC-9559-B84C7DC13A7E}"/>
+    <hyperlink ref="I13" r:id="rId17" xr:uid="{DFF6FEF9-F5C2-4E95-ADF7-B2FAE3DE850B}"/>
+    <hyperlink ref="I14" r:id="rId18" xr:uid="{97E949D6-A209-4081-A152-942084843042}"/>
+    <hyperlink ref="I16" r:id="rId19" xr:uid="{7DE90B3E-8711-4D96-98B8-7798310D4A2A}"/>
+    <hyperlink ref="I15" r:id="rId20" xr:uid="{5FDA68EF-0928-43E3-AB75-3CA34E289709}"/>
+    <hyperlink ref="I18" r:id="rId21" xr:uid="{B8B66BDE-99C7-42FB-92C2-5CAFEFE1A9EF}"/>
+    <hyperlink ref="I19" r:id="rId22" xr:uid="{88E87EE3-6DC4-46E4-AEA7-DD7795CA1270}"/>
+    <hyperlink ref="I20" r:id="rId23" xr:uid="{B636ACE3-4A7D-4A81-8D0D-9E12447C5069}"/>
+    <hyperlink ref="I21" r:id="rId24" xr:uid="{2B417871-5533-4B81-A637-DC3CE26B5460}"/>
+    <hyperlink ref="I22" r:id="rId25" xr:uid="{106C7162-77C3-4602-8FAB-DD162980D07E}"/>
+    <hyperlink ref="I23" r:id="rId26" xr:uid="{614B801B-CA5B-4116-9EA3-AE4B55A6428F}"/>
+    <hyperlink ref="I24" r:id="rId27" xr:uid="{BC44772C-0826-48A2-912B-50E51FCBC630}"/>
+    <hyperlink ref="I25" r:id="rId28" xr:uid="{00004B11-0749-4530-A82F-6434114310A4}"/>
+    <hyperlink ref="I26" r:id="rId29" xr:uid="{416BCD4D-A657-412B-A58B-2C1FAE74A65B}"/>
+    <hyperlink ref="I32" r:id="rId30" xr:uid="{046BB225-B5E3-47C4-A260-E7DF5739B2AB}"/>
+    <hyperlink ref="I33" r:id="rId31" xr:uid="{56777493-16A2-4EC1-B155-DEE463492E61}"/>
+    <hyperlink ref="I34" r:id="rId32" xr:uid="{7106046E-6C71-4CEA-8112-FB56CD5BCB61}"/>
+    <hyperlink ref="I35" r:id="rId33" xr:uid="{900DAE9C-09EF-4887-8B50-0F0ACD507DC4}"/>
+    <hyperlink ref="I36" r:id="rId34" xr:uid="{F0C9CCFE-DD05-4D75-9769-F351EE385880}"/>
+    <hyperlink ref="I37" r:id="rId35" xr:uid="{713BACB3-1A8D-47F4-A287-49DBE615A4D0}"/>
+    <hyperlink ref="I39" r:id="rId36" xr:uid="{D2A74AAA-A82F-485F-A00C-EC3F26E47727}"/>
+    <hyperlink ref="I40" r:id="rId37" xr:uid="{9649206E-9C15-469B-A73B-B40161178835}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId38"/>
 </worksheet>
 </file>
 
@@ -20334,7 +21180,7 @@
     </row>
     <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>70</v>
@@ -20352,15 +21198,15 @@
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
       <c r="I2" s="9" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>70</v>
@@ -20370,7 +21216,7 @@
         <v>48</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>74</v>
@@ -20380,21 +21226,21 @@
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>48</v>
@@ -20404,21 +21250,21 @@
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>48</v>
@@ -20428,21 +21274,21 @@
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="11" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>54</v>
@@ -20455,24 +21301,24 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>54</v>
@@ -20486,21 +21332,21 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>54</v>
@@ -20513,24 +21359,24 @@
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>54</v>
@@ -20544,21 +21390,21 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>54</v>
@@ -20572,21 +21418,21 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>48</v>
@@ -20596,21 +21442,21 @@
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>54</v>
@@ -20624,21 +21470,21 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>54</v>
@@ -20652,21 +21498,21 @@
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>54</v>
@@ -20680,21 +21526,21 @@
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>54</v>
@@ -20708,21 +21554,21 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>48</v>
@@ -20732,21 +21578,21 @@
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="11" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>54</v>
@@ -20760,21 +21606,21 @@
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>54</v>
@@ -20787,24 +21633,24 @@
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="10" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>54</v>
@@ -20817,24 +21663,24 @@
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10" t="s">
+        <v>949</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>953</v>
+      </c>
+      <c r="J19" s="10" t="s">
         <v>954</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>958</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>54</v>
@@ -20848,21 +21694,21 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>54</v>
@@ -20875,24 +21721,24 @@
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>48</v>
@@ -20902,21 +21748,21 @@
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>54</v>
@@ -20929,24 +21775,24 @@
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>54</v>
@@ -20960,21 +21806,21 @@
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>54</v>
@@ -20987,24 +21833,24 @@
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>54</v>
@@ -21017,24 +21863,24 @@
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>976</v>
+      </c>
+      <c r="J26" s="10" t="s">
         <v>977</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>981</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>54</v>
@@ -21048,21 +21894,21 @@
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>48</v>
@@ -21072,21 +21918,21 @@
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="11" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>54</v>
@@ -21100,21 +21946,21 @@
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>54</v>
@@ -21128,21 +21974,21 @@
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>54</v>
@@ -21156,21 +22002,21 @@
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="10" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>54</v>
@@ -21184,21 +22030,21 @@
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>54</v>
@@ -21211,24 +22057,24 @@
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>54</v>
@@ -21242,21 +22088,21 @@
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>54</v>
@@ -21270,21 +22116,21 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>48</v>
@@ -21294,21 +22140,21 @@
       <c r="G36" s="11"/>
       <c r="H36" s="11"/>
       <c r="I36" s="11" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>54</v>
@@ -21322,21 +22168,21 @@
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>54</v>
@@ -21350,21 +22196,21 @@
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>54</v>
@@ -21377,30 +22223,30 @@
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>74</v>
@@ -21408,21 +22254,21 @@
       <c r="G40" s="10"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>54</v>
@@ -21436,21 +22282,21 @@
       <c r="G41" s="10"/>
       <c r="H41" s="10"/>
       <c r="I41" s="10" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>54</v>
@@ -21464,21 +22310,21 @@
       <c r="G42" s="10"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>48</v>
@@ -21488,21 +22334,21 @@
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>54</v>
@@ -21516,21 +22362,21 @@
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>54</v>
@@ -21543,24 +22389,24 @@
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="10" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>54</v>
@@ -21574,21 +22420,21 @@
       <c r="G46" s="10"/>
       <c r="H46" s="10"/>
       <c r="I46" s="10" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="10" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>54</v>
@@ -21602,21 +22448,21 @@
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
       <c r="I47" s="10" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>54</v>
@@ -21630,21 +22476,21 @@
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
       <c r="I48" s="10" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="10" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>54</v>
@@ -21658,21 +22504,21 @@
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
       <c r="I49" s="10" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>54</v>
@@ -21685,24 +22531,24 @@
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="10" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>54</v>
@@ -21716,21 +22562,21 @@
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
       <c r="I51" s="10" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>54</v>
@@ -21744,21 +22590,21 @@
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
       <c r="I52" s="10" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>48</v>
@@ -21768,21 +22614,21 @@
       <c r="G53" s="11"/>
       <c r="H53" s="11"/>
       <c r="I53" s="11" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>54</v>
@@ -21796,21 +22642,21 @@
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
       <c r="I54" s="10" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>54</v>
@@ -21824,21 +22670,21 @@
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
       <c r="I55" s="10" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>54</v>
@@ -21852,21 +22698,21 @@
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
       <c r="I56" s="10" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>54</v>
@@ -21879,13 +22725,13 @@
       </c>
       <c r="G57" s="10"/>
       <c r="H57" s="10" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
@@ -21896,7 +22742,7 @@
         <v>70</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>54</v>
@@ -21912,13 +22758,13 @@
     </row>
     <row r="59" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>54</v>
@@ -21932,21 +22778,21 @@
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
       <c r="I59" s="10" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>54</v>
@@ -21960,21 +22806,21 @@
       <c r="G60" s="10"/>
       <c r="H60" s="10"/>
       <c r="I60" s="10" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>48</v>
@@ -21984,21 +22830,21 @@
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
       <c r="I61" s="11" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>54</v>
@@ -22012,21 +22858,21 @@
       <c r="G62" s="10"/>
       <c r="H62" s="10"/>
       <c r="I62" s="10" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="10" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>54</v>
@@ -22039,24 +22885,24 @@
       </c>
       <c r="G63" s="10"/>
       <c r="H63" s="10" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>54</v>
@@ -22069,24 +22915,24 @@
       </c>
       <c r="G64" s="10"/>
       <c r="H64" s="10" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>54</v>
@@ -22100,21 +22946,21 @@
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
       <c r="I65" s="10" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>54</v>
@@ -22128,21 +22974,21 @@
       <c r="G66" s="10"/>
       <c r="H66" s="10"/>
       <c r="I66" s="10" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="10" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>54</v>
@@ -22156,21 +23002,21 @@
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
       <c r="I67" s="10" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>54</v>
@@ -22184,21 +23030,21 @@
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
       <c r="I68" s="10" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="10" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B69" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>54</v>
@@ -22212,21 +23058,21 @@
       <c r="G69" s="10"/>
       <c r="H69" s="10"/>
       <c r="I69" s="10" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>54</v>
@@ -22240,21 +23086,21 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
       <c r="I70" s="10" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>48</v>
@@ -22264,21 +23110,21 @@
       <c r="G71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="11" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>54</v>
@@ -22292,27 +23138,27 @@
       <c r="G72" s="10"/>
       <c r="H72" s="10"/>
       <c r="I72" s="10" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="10" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>74</v>
@@ -22320,21 +23166,21 @@
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
       <c r="I73" s="10" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>54</v>
@@ -22348,21 +23194,21 @@
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
       <c r="I74" s="10" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="10" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>54</v>
@@ -22375,24 +23221,24 @@
       </c>
       <c r="G75" s="10"/>
       <c r="H75" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>54</v>
@@ -22406,21 +23252,21 @@
       <c r="G76" s="10"/>
       <c r="H76" s="10"/>
       <c r="I76" s="10" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="10" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>54</v>
@@ -22434,21 +23280,21 @@
       <c r="G77" s="10"/>
       <c r="H77" s="10"/>
       <c r="I77" s="10" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>54</v>
@@ -22461,24 +23307,24 @@
       </c>
       <c r="G78" s="10"/>
       <c r="H78" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>54</v>
@@ -22492,21 +23338,21 @@
       <c r="G79" s="10"/>
       <c r="H79" s="10"/>
       <c r="I79" s="10" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>54</v>
@@ -22520,21 +23366,21 @@
       <c r="G80" s="10"/>
       <c r="H80" s="10"/>
       <c r="I80" s="10" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" s="11" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>48</v>
@@ -22544,21 +23390,21 @@
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
       <c r="I81" s="11" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="J81" s="11" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>54</v>
@@ -22572,21 +23418,21 @@
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="10" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>54</v>
@@ -22599,24 +23445,24 @@
       </c>
       <c r="G83" s="10"/>
       <c r="H83" s="10" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>54</v>
@@ -22630,21 +23476,21 @@
       <c r="G84" s="10"/>
       <c r="H84" s="10"/>
       <c r="I84" s="10" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>54</v>
@@ -22657,24 +23503,24 @@
       </c>
       <c r="G85" s="10"/>
       <c r="H85" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>54</v>
@@ -22687,24 +23533,24 @@
       </c>
       <c r="G86" s="10"/>
       <c r="H86" s="10" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>54</v>
@@ -22718,21 +23564,21 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="10" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>54</v>
@@ -22746,21 +23592,21 @@
       <c r="G88" s="10"/>
       <c r="H88" s="10"/>
       <c r="I88" s="10" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="10" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>54</v>
@@ -22774,21 +23620,21 @@
       <c r="G89" s="10"/>
       <c r="H89" s="10"/>
       <c r="I89" s="10" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" s="11" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>48</v>
@@ -22798,21 +23644,21 @@
       <c r="G90" s="11"/>
       <c r="H90" s="11"/>
       <c r="I90" s="11" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="10" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>54</v>
@@ -22826,21 +23672,21 @@
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
       <c r="I91" s="10" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>54</v>
@@ -22854,21 +23700,21 @@
       <c r="G92" s="10"/>
       <c r="H92" s="10"/>
       <c r="I92" s="10" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="10" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>54</v>
@@ -22881,24 +23727,24 @@
       </c>
       <c r="G93" s="10"/>
       <c r="H93" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I93" s="10" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>54</v>
@@ -22912,21 +23758,21 @@
       <c r="G94" s="10"/>
       <c r="H94" s="10"/>
       <c r="I94" s="10" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>54</v>
@@ -22939,30 +23785,30 @@
       </c>
       <c r="G95" s="10"/>
       <c r="H95" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>74</v>
@@ -22970,21 +23816,21 @@
       <c r="G96" s="10"/>
       <c r="H96" s="10"/>
       <c r="I96" s="10" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>54</v>
@@ -22997,24 +23843,24 @@
       </c>
       <c r="G97" s="10"/>
       <c r="H97" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I97" s="10" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>54</v>
@@ -23028,21 +23874,21 @@
       <c r="G98" s="10"/>
       <c r="H98" s="10"/>
       <c r="I98" s="10" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>54</v>
@@ -23056,21 +23902,21 @@
       <c r="G99" s="10"/>
       <c r="H99" s="10"/>
       <c r="I99" s="10" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>54</v>
@@ -23083,24 +23929,24 @@
       </c>
       <c r="G100" s="10"/>
       <c r="H100" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="10" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>54</v>
@@ -23114,21 +23960,21 @@
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
       <c r="I101" s="10" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>54</v>
@@ -23142,10 +23988,10 @@
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
       <c r="I102" s="10" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
@@ -23160,19 +24006,19 @@
         <v>48</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="9"/>
       <c r="J103" s="9" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A104" s="11" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>103</v>
@@ -23191,18 +24037,18 @@
         <v>123</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" s="11" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>48</v>
@@ -23212,21 +24058,21 @@
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
       <c r="I105" s="11" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>54</v>
@@ -23240,21 +24086,21 @@
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
       <c r="I106" s="10" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="10" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>54</v>
@@ -23267,24 +24113,24 @@
       </c>
       <c r="G107" s="10"/>
       <c r="H107" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>54</v>
@@ -23298,21 +24144,21 @@
       <c r="G108" s="10"/>
       <c r="H108" s="10"/>
       <c r="I108" s="10" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="10" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>54</v>
@@ -23326,27 +24172,27 @@
       <c r="G109" s="10"/>
       <c r="H109" s="10"/>
       <c r="I109" s="10" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="F110" s="10" t="s">
         <v>74</v>
@@ -23354,21 +24200,21 @@
       <c r="G110" s="10"/>
       <c r="H110" s="10"/>
       <c r="I110" s="10" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="10" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>54</v>
@@ -23381,24 +24227,24 @@
       </c>
       <c r="G111" s="10"/>
       <c r="H111" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A112" s="11" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>48</v>
@@ -23408,21 +24254,21 @@
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
       <c r="I112" s="11" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="J112" s="11" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="B113" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>54</v>
@@ -23436,21 +24282,21 @@
       <c r="G113" s="10"/>
       <c r="H113" s="10"/>
       <c r="I113" s="10" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="B114" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>54</v>
@@ -23463,24 +24309,24 @@
       </c>
       <c r="G114" s="10"/>
       <c r="H114" s="10" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="10" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="B115" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>54</v>
@@ -23493,24 +24339,24 @@
       </c>
       <c r="G115" s="10"/>
       <c r="H115" s="10" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>54</v>
@@ -23524,21 +24370,21 @@
       <c r="G116" s="10"/>
       <c r="H116" s="10"/>
       <c r="I116" s="10" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="10" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="B117" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>54</v>
@@ -23552,21 +24398,21 @@
       <c r="G117" s="10"/>
       <c r="H117" s="10"/>
       <c r="I117" s="10" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A118" s="11" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>48</v>
@@ -23576,21 +24422,21 @@
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
       <c r="I118" s="11" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="J118" s="11" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="B119" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>54</v>
@@ -23604,21 +24450,21 @@
       <c r="G119" s="10"/>
       <c r="H119" s="10"/>
       <c r="I119" s="10" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="D120" s="10" t="s">
         <v>54</v>
@@ -23632,10 +24478,10 @@
       <c r="G120" s="10"/>
       <c r="H120" s="10"/>
       <c r="I120" s="10" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.35">
@@ -23646,7 +24492,7 @@
         <v>70</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>54</v>
@@ -23662,13 +24508,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="B122" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>54</v>
@@ -23684,13 +24530,13 @@
     </row>
     <row r="123" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="B123" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>54</v>
@@ -23704,21 +24550,21 @@
       <c r="G123" s="10"/>
       <c r="H123" s="10"/>
       <c r="I123" s="10" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B124" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>54</v>
@@ -23731,24 +24577,24 @@
       </c>
       <c r="G124" s="10"/>
       <c r="H124" s="10" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A125" s="11" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>103</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="D125" s="11" t="s">
         <v>48</v>
@@ -23758,21 +24604,21 @@
       <c r="G125" s="11"/>
       <c r="H125" s="11"/>
       <c r="I125" s="11" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="J125" s="11" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="B126" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>54</v>
@@ -23786,21 +24632,21 @@
       <c r="G126" s="10"/>
       <c r="H126" s="10"/>
       <c r="I126" s="10" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="B127" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>54</v>
@@ -23814,10 +24660,10 @@
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
       <c r="I127" s="10" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.35">
@@ -23828,7 +24674,7 @@
         <v>70</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>54</v>
@@ -23844,13 +24690,13 @@
     </row>
     <row r="129" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B129" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>54</v>
@@ -23864,21 +24710,21 @@
       <c r="G129" s="10"/>
       <c r="H129" s="10"/>
       <c r="I129" s="10" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="B130" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>54</v>
@@ -23892,21 +24738,21 @@
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
       <c r="I130" s="10" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="J130" s="10" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="B131" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>54</v>
@@ -23920,21 +24766,21 @@
       <c r="G131" s="10"/>
       <c r="H131" s="10"/>
       <c r="I131" s="10" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="J131" s="10" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="B132" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C132" s="10" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="D132" s="10" t="s">
         <v>54</v>
@@ -23948,10 +24794,10 @@
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
       <c r="I132" s="10" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="J132" s="10" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
     </row>
   </sheetData>
